--- a/vignettes/dictionary_conversion_filled.xlsx
+++ b/vignettes/dictionary_conversion_filled.xlsx
@@ -12,9 +12,8 @@
     <sheet name="variable_pattern" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="category_pattern" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="manual_matches" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="unit_conversion" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="national_suffixes_reference" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="category_reference" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="national_suffixes_reference" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="category_reference" sheetId="6" state="visible" r:id="rId8"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -26,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1862" uniqueCount="631">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1857" uniqueCount="629">
   <si>
     <t xml:space="preserve">Step</t>
   </si>
@@ -1904,12 +1903,6 @@
   </si>
   <si>
     <t xml:space="preserve">Aliments concentrés pour volailles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">conversion_factor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">notes</t>
   </si>
   <si>
     <t xml:space="preserve">national_suffix</t>
@@ -2212,20 +2205,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table7" displayName="Table7" ref="A1:E2" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:E2"/>
-  <tableColumns count="5">
-    <tableColumn id="1" name="national_code"/>
-    <tableColumn id="2" name="pattern_national"/>
-    <tableColumn id="3" name="conversion_factor"/>
-    <tableColumn id="4" name="Group"/>
-    <tableColumn id="5" name="notes"/>
-  </tableColumns>
-</table>
-</file>
-
-<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table8" displayName="Table8" ref="A1:B59" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table8" displayName="Table8" ref="A1:B59" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <autoFilter ref="A1:B59"/>
   <tableColumns count="2">
     <tableColumn id="1" name="Group"/>
@@ -2234,8 +2214,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="Table9" displayName="Table9" ref="A1:D197" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table9" displayName="Table9" ref="A1:D197" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <autoFilter ref="A1:D197"/>
   <tableColumns count="4">
     <tableColumn id="1" name="FADN_code_letter"/>
@@ -5962,6 +5942,7 @@
   <dimension ref="A1:J35"/>
   <sheetFormatPr defaultColWidth="10.453125" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="19.1"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="48.55"/>
   </cols>
   <sheetData>
@@ -6954,24 +6935,479 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:B59"/>
   <sheetFormatPr defaultColWidth="10.453125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>160</v>
+        <v>11</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C1" s="1" t="s">
         <v>590</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1" s="1" t="s">
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>591</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>622</v>
       </c>
     </row>
   </sheetData>
@@ -6993,500 +7429,6 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B59"/>
-  <sheetFormatPr defaultColWidth="10.453125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>624</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <tableParts>
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
   <dimension ref="A1:D197"/>
   <sheetFormatPr defaultColWidth="10.453125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
@@ -9466,7 +9408,7 @@
         <v>173</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="C187" s="2" t="s">
         <v>20</v>
@@ -9477,7 +9419,7 @@
         <v>175</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="C188" s="2" t="s">
         <v>20</v>
@@ -9496,7 +9438,7 @@
         <v>177</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="C190" s="2" t="s">
         <v>20</v>
@@ -9523,7 +9465,7 @@
         <v>162</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="C193" s="2" t="s">
         <v>20</v>
@@ -9542,7 +9484,7 @@
         <v>170</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="C195" s="2" t="s">
         <v>20</v>
@@ -9553,7 +9495,7 @@
         <v>166</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="C196" s="2" t="s">
         <v>20</v>
@@ -9564,7 +9506,7 @@
         <v>168</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="C197" s="2" t="s">
         <v>20</v>

--- a/vignettes/dictionary_conversion_filled.xlsx
+++ b/vignettes/dictionary_conversion_filled.xlsx
@@ -5942,7 +5942,7 @@
   <dimension ref="A1:J35"/>
   <sheetFormatPr defaultColWidth="10.453125" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="19.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="19.1"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="48.55"/>
   </cols>
   <sheetData>
@@ -6882,7 +6882,7 @@
         <v>445</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="J34" s="2"/>
     </row>

--- a/vignettes/dictionary_conversion_filled.xlsx
+++ b/vignettes/dictionary_conversion_filled.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="instructions" sheetId="1" state="visible" r:id="rId3"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1862" uniqueCount="631">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2036" uniqueCount="764">
   <si>
     <t xml:space="preserve">Step</t>
   </si>
@@ -514,60 +514,96 @@
     <t xml:space="preserve">allocation_key</t>
   </si>
   <si>
+    <t xml:space="preserve">national_description</t>
+  </si>
+  <si>
     <t xml:space="preserve">PMLKCOW</t>
   </si>
   <si>
     <t xml:space="preserve">021</t>
   </si>
   <si>
+    <t xml:space="preserve">Lait de vache</t>
+  </si>
+  <si>
     <t xml:space="preserve">031</t>
   </si>
   <si>
+    <t xml:space="preserve">Fromages mixtes vache/brebis</t>
+  </si>
+  <si>
     <t xml:space="preserve">032</t>
   </si>
   <si>
+    <t xml:space="preserve">Fromages mixtes vache/chèvre</t>
+  </si>
+  <si>
     <t xml:space="preserve">PMLKSHEP</t>
   </si>
   <si>
     <t xml:space="preserve">041</t>
   </si>
   <si>
+    <t xml:space="preserve">Lait de brebis</t>
+  </si>
+  <si>
     <t xml:space="preserve">PWOOL</t>
   </si>
   <si>
     <t xml:space="preserve">043</t>
   </si>
   <si>
+    <t xml:space="preserve">Laine d'ovins</t>
+  </si>
+  <si>
     <t xml:space="preserve">PMLKGOAT</t>
   </si>
   <si>
     <t xml:space="preserve">051</t>
   </si>
   <si>
+    <t xml:space="preserve">Lait de chèvre</t>
+  </si>
+  <si>
     <t xml:space="preserve">074</t>
   </si>
   <si>
+    <t xml:space="preserve">Viande de poule, poulet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEGGH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Œufs de poule</t>
+  </si>
+  <si>
     <t xml:space="preserve">PEGGC</t>
   </si>
   <si>
-    <t xml:space="preserve">076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PEGGH</t>
-  </si>
-  <si>
     <t xml:space="preserve">078</t>
   </si>
   <si>
+    <t xml:space="preserve">Autres produits de poule</t>
+  </si>
+  <si>
     <t xml:space="preserve">PHONEY</t>
   </si>
   <si>
     <t xml:space="preserve">090</t>
   </si>
   <si>
+    <t xml:space="preserve">Miel</t>
+  </si>
+  <si>
     <t xml:space="preserve">096</t>
   </si>
   <si>
+    <t xml:space="preserve">Fumier, lisier</t>
+  </si>
+  <si>
     <t xml:space="preserve">PANIMPRDOTH</t>
   </si>
   <si>
@@ -610,84 +646,132 @@
     <t xml:space="preserve">111</t>
   </si>
   <si>
+    <t xml:space="preserve">Blé tendre</t>
+  </si>
+  <si>
     <t xml:space="preserve">CWHTD</t>
   </si>
   <si>
     <t xml:space="preserve">112</t>
   </si>
   <si>
+    <t xml:space="preserve">Blé dur</t>
+  </si>
+  <si>
     <t xml:space="preserve">CRYE</t>
   </si>
   <si>
     <t xml:space="preserve">113</t>
   </si>
   <si>
+    <t xml:space="preserve">Seigle</t>
+  </si>
+  <si>
     <t xml:space="preserve">CBRL</t>
   </si>
   <si>
     <t xml:space="preserve">114</t>
   </si>
   <si>
+    <t xml:space="preserve">Orge de printemps</t>
+  </si>
+  <si>
     <t xml:space="preserve">115</t>
   </si>
   <si>
+    <t xml:space="preserve">Orge d’hiver et escourgeon</t>
+  </si>
+  <si>
     <t xml:space="preserve">COAT</t>
   </si>
   <si>
     <t xml:space="preserve">116</t>
   </si>
   <si>
+    <t xml:space="preserve">Avoine</t>
+  </si>
+  <si>
     <t xml:space="preserve">CCEROTH</t>
   </si>
   <si>
     <t xml:space="preserve">117</t>
   </si>
   <si>
+    <t xml:space="preserve">Mélange céréales d'été</t>
+  </si>
+  <si>
     <t xml:space="preserve">CMZ</t>
   </si>
   <si>
     <t xml:space="preserve">118</t>
   </si>
   <si>
+    <t xml:space="preserve">Maïs grain</t>
+  </si>
+  <si>
     <t xml:space="preserve">CRICE</t>
   </si>
   <si>
     <t xml:space="preserve">120</t>
   </si>
   <si>
+    <t xml:space="preserve">Riz</t>
+  </si>
+  <si>
     <t xml:space="preserve">121</t>
   </si>
   <si>
+    <t xml:space="preserve">Triticale</t>
+  </si>
+  <si>
     <t xml:space="preserve">122</t>
   </si>
   <si>
+    <t xml:space="preserve">Autres céréales</t>
+  </si>
+  <si>
     <t xml:space="preserve">CPOT</t>
   </si>
   <si>
     <t xml:space="preserve">201</t>
   </si>
   <si>
+    <t xml:space="preserve">Pomme de terre primeur et nouvelle</t>
+  </si>
+  <si>
     <t xml:space="preserve">CPOTOTH</t>
   </si>
   <si>
     <t xml:space="preserve">202</t>
   </si>
   <si>
+    <t xml:space="preserve">Pomme de terre de conservation</t>
+  </si>
+  <si>
     <t xml:space="preserve">203</t>
   </si>
   <si>
+    <t xml:space="preserve">Pomme de terre de plant</t>
+  </si>
+  <si>
     <t xml:space="preserve">CPOTST</t>
   </si>
   <si>
     <t xml:space="preserve">204</t>
   </si>
   <si>
+    <t xml:space="preserve">Pomme de terre de féculerie</t>
+  </si>
+  <si>
     <t xml:space="preserve">CSUGBT</t>
   </si>
   <si>
     <t xml:space="preserve">213</t>
   </si>
   <si>
+    <t xml:space="preserve">Betterave sucrière</t>
+  </si>
+  <si>
     <t xml:space="preserve">CSUGBTTOP</t>
   </si>
   <si>
@@ -697,105 +781,162 @@
     <t xml:space="preserve">214</t>
   </si>
   <si>
+    <t xml:space="preserve">Fève et féverole</t>
+  </si>
+  <si>
     <t xml:space="preserve">CPEA</t>
   </si>
   <si>
     <t xml:space="preserve">215</t>
   </si>
   <si>
+    <t xml:space="preserve">Pois sec pour l'alimentation humaine</t>
+  </si>
+  <si>
     <t xml:space="preserve">216</t>
   </si>
   <si>
+    <t xml:space="preserve">Lentille</t>
+  </si>
+  <si>
     <t xml:space="preserve">CLNTL</t>
   </si>
   <si>
     <t xml:space="preserve">217</t>
   </si>
   <si>
+    <t xml:space="preserve">Pois protéagineux</t>
+  </si>
+  <si>
     <t xml:space="preserve">218</t>
   </si>
   <si>
+    <t xml:space="preserve">Lupin doux</t>
+  </si>
+  <si>
     <t xml:space="preserve">219</t>
   </si>
   <si>
+    <t xml:space="preserve">Pois chiche et vesce</t>
+  </si>
+  <si>
     <t xml:space="preserve">CCRPPROTOTH</t>
   </si>
   <si>
     <t xml:space="preserve">220</t>
   </si>
   <si>
+    <t xml:space="preserve">Autres légumes secs</t>
+  </si>
+  <si>
     <t xml:space="preserve">CSNFL</t>
   </si>
   <si>
     <t xml:space="preserve">221</t>
   </si>
   <si>
+    <t xml:space="preserve">Tournesol</t>
+  </si>
+  <si>
     <t xml:space="preserve">CRAPE</t>
   </si>
   <si>
     <t xml:space="preserve">222</t>
   </si>
   <si>
+    <t xml:space="preserve">Colza</t>
+  </si>
+  <si>
     <t xml:space="preserve">CSOYA</t>
   </si>
   <si>
     <t xml:space="preserve">223</t>
   </si>
   <si>
+    <t xml:space="preserve">Soja</t>
+  </si>
+  <si>
     <t xml:space="preserve">CLINSED</t>
   </si>
   <si>
     <t xml:space="preserve">225</t>
   </si>
   <si>
+    <t xml:space="preserve">Lin oléagineux</t>
+  </si>
+  <si>
     <t xml:space="preserve">CCRPOILOTH</t>
   </si>
   <si>
     <t xml:space="preserve">229</t>
   </si>
   <si>
+    <t xml:space="preserve">Autres oléagineux (ricin, etc.)</t>
+  </si>
+  <si>
     <t xml:space="preserve">CHEMP</t>
   </si>
   <si>
     <t xml:space="preserve">231</t>
   </si>
   <si>
+    <t xml:space="preserve">Chanvre</t>
+  </si>
+  <si>
     <t xml:space="preserve">CFLAX</t>
   </si>
   <si>
     <t xml:space="preserve">232</t>
   </si>
   <si>
+    <t xml:space="preserve">Lin à fibres</t>
+  </si>
+  <si>
     <t xml:space="preserve">CHOP</t>
   </si>
   <si>
     <t xml:space="preserve">241</t>
   </si>
   <si>
+    <t xml:space="preserve">Houblon</t>
+  </si>
+  <si>
     <t xml:space="preserve">CTOBAC</t>
   </si>
   <si>
     <t xml:space="preserve">242</t>
   </si>
   <si>
+    <t xml:space="preserve">Tabac</t>
+  </si>
+  <si>
     <t xml:space="preserve">CSUGCN</t>
   </si>
   <si>
     <t xml:space="preserve">245</t>
   </si>
   <si>
+    <t xml:space="preserve">Canne à sucre</t>
+  </si>
+  <si>
     <t xml:space="preserve">CMEDIC</t>
   </si>
   <si>
     <t xml:space="preserve">251</t>
   </si>
   <si>
+    <t xml:space="preserve">Plantes médicinales, condimentaires, aromatiques</t>
+  </si>
+  <si>
     <t xml:space="preserve">CCOTN</t>
   </si>
   <si>
     <t xml:space="preserve">252</t>
   </si>
   <si>
+    <t xml:space="preserve">Autres cultures industrielles</t>
+  </si>
+  <si>
     <t xml:space="preserve">CCRPINDOTH</t>
   </si>
   <si>
@@ -808,6 +949,9 @@
     <t xml:space="preserve">311</t>
   </si>
   <si>
+    <t xml:space="preserve">Plantes sarclées fourragères</t>
+  </si>
+  <si>
     <t xml:space="preserve">CFODRTBR</t>
   </si>
   <si>
@@ -817,33 +961,51 @@
     <t xml:space="preserve">321</t>
   </si>
   <si>
+    <t xml:space="preserve">Maïs fourrage</t>
+  </si>
+  <si>
     <t xml:space="preserve">CCRPPROT_X</t>
   </si>
   <si>
     <t xml:space="preserve">323</t>
   </si>
   <si>
+    <t xml:space="preserve">Luzerne pour déshydratation</t>
+  </si>
+  <si>
     <t xml:space="preserve">324</t>
   </si>
   <si>
+    <t xml:space="preserve">Autres fourrages artificiels</t>
+  </si>
+  <si>
     <t xml:space="preserve">CGRSTMP</t>
   </si>
   <si>
     <t xml:space="preserve">331</t>
   </si>
   <si>
+    <t xml:space="preserve">Prairies temporaires</t>
+  </si>
+  <si>
     <t xml:space="preserve">CGRSXRG</t>
   </si>
   <si>
     <t xml:space="preserve">341</t>
   </si>
   <si>
+    <t xml:space="preserve">Prairies permanentes</t>
+  </si>
+  <si>
     <t xml:space="preserve">CRG</t>
   </si>
   <si>
     <t xml:space="preserve">342</t>
   </si>
   <si>
+    <t xml:space="preserve">Parcours, landes et alpages productifs, pacages publics</t>
+  </si>
+  <si>
     <t xml:space="preserve">CARALNDSED</t>
   </si>
   <si>
@@ -856,12 +1018,18 @@
     <t xml:space="preserve">371</t>
   </si>
   <si>
+    <t xml:space="preserve">Semences d'herbe</t>
+  </si>
+  <si>
     <t xml:space="preserve">CCFL</t>
   </si>
   <si>
     <t xml:space="preserve">410</t>
   </si>
   <si>
+    <t xml:space="preserve">Ensemble des légumes frais</t>
+  </si>
+  <si>
     <t xml:space="preserve">CCRNSWT</t>
   </si>
   <si>
@@ -904,15 +1072,24 @@
     <t xml:space="preserve">511</t>
   </si>
   <si>
+    <t xml:space="preserve">Pomme de table</t>
+  </si>
+  <si>
     <t xml:space="preserve">512</t>
   </si>
   <si>
+    <t xml:space="preserve">Pomme à cidre</t>
+  </si>
+  <si>
     <t xml:space="preserve">CPEAR</t>
   </si>
   <si>
     <t xml:space="preserve">513</t>
   </si>
   <si>
+    <t xml:space="preserve">Poire de table</t>
+  </si>
+  <si>
     <t xml:space="preserve">521</t>
   </si>
   <si>
@@ -922,27 +1099,45 @@
     <t xml:space="preserve">524</t>
   </si>
   <si>
+    <t xml:space="preserve">Pêche, brugnon</t>
+  </si>
+  <si>
     <t xml:space="preserve">CNUT</t>
   </si>
   <si>
     <t xml:space="preserve">532</t>
   </si>
   <si>
+    <t xml:space="preserve">Amande</t>
+  </si>
+  <si>
     <t xml:space="preserve">533</t>
   </si>
   <si>
+    <t xml:space="preserve">Châtaigne</t>
+  </si>
+  <si>
     <t xml:space="preserve">534</t>
   </si>
   <si>
+    <t xml:space="preserve">Noix</t>
+  </si>
+  <si>
     <t xml:space="preserve">535</t>
   </si>
   <si>
+    <t xml:space="preserve">Autres fruits à coque (noisettes, etc.)</t>
+  </si>
+  <si>
     <t xml:space="preserve">CBERRY</t>
   </si>
   <si>
     <t xml:space="preserve">541</t>
   </si>
   <si>
+    <t xml:space="preserve">Groseille</t>
+  </si>
+  <si>
     <t xml:space="preserve">542</t>
   </si>
   <si>
@@ -955,60 +1150,96 @@
     <t xml:space="preserve">544</t>
   </si>
   <si>
+    <t xml:space="preserve">Avocat</t>
+  </si>
+  <si>
     <t xml:space="preserve">545</t>
   </si>
   <si>
+    <t xml:space="preserve">Figue</t>
+  </si>
+  <si>
     <t xml:space="preserve">CFRUTTMP</t>
   </si>
   <si>
     <t xml:space="preserve">547</t>
   </si>
   <si>
+    <t xml:space="preserve">Autres fruits</t>
+  </si>
+  <si>
     <t xml:space="preserve">548</t>
   </si>
   <si>
+    <t xml:space="preserve">Banane</t>
+  </si>
+  <si>
     <t xml:space="preserve">549</t>
   </si>
   <si>
+    <t xml:space="preserve">Ananas</t>
+  </si>
+  <si>
     <t xml:space="preserve">550</t>
   </si>
   <si>
+    <t xml:space="preserve">Mangue</t>
+  </si>
+  <si>
     <t xml:space="preserve">CORANG</t>
   </si>
   <si>
     <t xml:space="preserve">551</t>
   </si>
   <si>
+    <t xml:space="preserve">Orange</t>
+  </si>
+  <si>
     <t xml:space="preserve">CCITRSML</t>
   </si>
   <si>
     <t xml:space="preserve">554</t>
   </si>
   <si>
+    <t xml:space="preserve">Mandarine, clémentine et similaires</t>
+  </si>
+  <si>
     <t xml:space="preserve">CLMON</t>
   </si>
   <si>
     <t xml:space="preserve">555</t>
   </si>
   <si>
+    <t xml:space="preserve">Citron</t>
+  </si>
+  <si>
     <t xml:space="preserve">CCITROTH</t>
   </si>
   <si>
     <t xml:space="preserve">557</t>
   </si>
   <si>
+    <t xml:space="preserve">Autres agrumes</t>
+  </si>
+  <si>
     <t xml:space="preserve">COLV</t>
   </si>
   <si>
     <t xml:space="preserve">561</t>
   </si>
   <si>
+    <t xml:space="preserve">Olive de table</t>
+  </si>
+  <si>
     <t xml:space="preserve">COLVFR</t>
   </si>
   <si>
     <t xml:space="preserve">562</t>
   </si>
   <si>
+    <t xml:space="preserve">Olive pour l'huile</t>
+  </si>
+  <si>
     <t xml:space="preserve">COLVGROV_X</t>
   </si>
   <si>
@@ -1021,9 +1252,15 @@
     <t xml:space="preserve">620</t>
   </si>
   <si>
+    <t xml:space="preserve">Vigne raisin de table</t>
+  </si>
+  <si>
     <t xml:space="preserve">621</t>
   </si>
   <si>
+    <t xml:space="preserve">Raisin de table</t>
+  </si>
+  <si>
     <t xml:space="preserve">CRAISIN</t>
   </si>
   <si>
@@ -1033,6 +1270,9 @@
     <t xml:space="preserve">630</t>
   </si>
   <si>
+    <t xml:space="preserve">Vignes AOP</t>
+  </si>
+  <si>
     <t xml:space="preserve">CVIN_X</t>
   </si>
   <si>
@@ -1042,48 +1282,72 @@
     <t xml:space="preserve">631</t>
   </si>
   <si>
+    <t xml:space="preserve">Raisin AOP</t>
+  </si>
+  <si>
     <t xml:space="preserve">CGRPWINPGI</t>
   </si>
   <si>
     <t xml:space="preserve">670</t>
   </si>
   <si>
+    <t xml:space="preserve">Vignes à vin IGP/ de pays</t>
+  </si>
+  <si>
     <t xml:space="preserve">CWINEPGI</t>
   </si>
   <si>
     <t xml:space="preserve">671</t>
   </si>
   <si>
+    <t xml:space="preserve">Raisin à vin IGP/ de pays</t>
+  </si>
+  <si>
     <t xml:space="preserve">CGRPWINOTH</t>
   </si>
   <si>
     <t xml:space="preserve">675</t>
   </si>
   <si>
+    <t xml:space="preserve">Vignes à vin sans IG ou VSIG/ de table</t>
+  </si>
+  <si>
     <t xml:space="preserve">CWINEOTH</t>
   </si>
   <si>
     <t xml:space="preserve">676</t>
   </si>
   <si>
+    <t xml:space="preserve">Raisin à vin sans IG ou VSIG/ de table</t>
+  </si>
+  <si>
     <t xml:space="preserve">CMUSH</t>
   </si>
   <si>
     <t xml:space="preserve">711</t>
   </si>
   <si>
+    <t xml:space="preserve">Champignons</t>
+  </si>
+  <si>
     <t xml:space="preserve">CFRUTBER_X</t>
   </si>
   <si>
     <t xml:space="preserve">721</t>
   </si>
   <si>
+    <t xml:space="preserve">Pépinières fruitières, plants fruitiers</t>
+  </si>
+  <si>
     <t xml:space="preserve">CARAOTH</t>
   </si>
   <si>
     <t xml:space="preserve">741</t>
   </si>
   <si>
+    <t xml:space="preserve">Autres cultures de terres arables</t>
+  </si>
+  <si>
     <t xml:space="preserve">COLVBY</t>
   </si>
   <si>
@@ -1093,193 +1357,328 @@
     <t xml:space="preserve">912</t>
   </si>
   <si>
+    <t xml:space="preserve">Chevaux</t>
+  </si>
+  <si>
     <t xml:space="preserve">913</t>
   </si>
   <si>
+    <t xml:space="preserve">Ânes, mulets, bardots</t>
+  </si>
+  <si>
     <t xml:space="preserve">LBOV1</t>
   </si>
   <si>
     <t xml:space="preserve">921</t>
   </si>
   <si>
+    <t xml:space="preserve">Veaux de batterie</t>
+  </si>
+  <si>
     <t xml:space="preserve">922</t>
   </si>
   <si>
+    <t xml:space="preserve">Autres veaux de boucherie</t>
+  </si>
+  <si>
     <t xml:space="preserve">LBOV1_2F</t>
   </si>
   <si>
     <t xml:space="preserve">925</t>
   </si>
   <si>
+    <t xml:space="preserve">Génisses de 1 à 2 ans</t>
+  </si>
+  <si>
     <t xml:space="preserve">LHEIFBRE</t>
   </si>
   <si>
     <t xml:space="preserve">927</t>
   </si>
   <si>
+    <t xml:space="preserve">Génisses d’élevage de 2 ans et plus</t>
+  </si>
+  <si>
     <t xml:space="preserve">LHEIFFAT</t>
   </si>
   <si>
     <t xml:space="preserve">928</t>
   </si>
   <si>
+    <t xml:space="preserve">Génisses de boucherie de 2 ans et plus</t>
+  </si>
+  <si>
     <t xml:space="preserve">LCOWDAIR</t>
   </si>
   <si>
     <t xml:space="preserve">929</t>
   </si>
   <si>
+    <t xml:space="preserve">Vaches laitières</t>
+  </si>
+  <si>
     <t xml:space="preserve">LCOWOTH</t>
   </si>
   <si>
     <t xml:space="preserve">930</t>
   </si>
   <si>
+    <t xml:space="preserve">Vaches allaitantes</t>
+  </si>
+  <si>
     <t xml:space="preserve">931</t>
   </si>
   <si>
+    <t xml:space="preserve">Veaux de 8 jours, à remettre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Broutards</t>
+  </si>
+  <si>
     <t xml:space="preserve">933</t>
   </si>
   <si>
+    <t xml:space="preserve">Autres bovins de moins de 1 an</t>
+  </si>
+  <si>
     <t xml:space="preserve">LBOV1_2M</t>
   </si>
   <si>
     <t xml:space="preserve">934</t>
   </si>
   <si>
+    <t xml:space="preserve">Bovins mâles de 1 à 2 ans maigres</t>
+  </si>
+  <si>
     <t xml:space="preserve">935</t>
   </si>
   <si>
+    <t xml:space="preserve">Bovins mâles de 1 à 2 ans gras</t>
+  </si>
+  <si>
     <t xml:space="preserve">LBOV2</t>
   </si>
   <si>
     <t xml:space="preserve">936</t>
   </si>
   <si>
+    <t xml:space="preserve">Taureaux reproducteurs de 2 ans et plus</t>
+  </si>
+  <si>
     <t xml:space="preserve">937</t>
   </si>
   <si>
+    <t xml:space="preserve">Autres bovins mâles de 2 ans et plus</t>
+  </si>
+  <si>
     <t xml:space="preserve">LEWEBRE</t>
   </si>
   <si>
     <t xml:space="preserve">941</t>
   </si>
   <si>
+    <t xml:space="preserve">Brebis laitières</t>
+  </si>
+  <si>
     <t xml:space="preserve">942</t>
   </si>
   <si>
+    <t xml:space="preserve">Brebis allaitantes</t>
+  </si>
+  <si>
     <t xml:space="preserve">LSHEPOTH</t>
   </si>
   <si>
     <t xml:space="preserve">944</t>
   </si>
   <si>
+    <t xml:space="preserve">Agnelles</t>
+  </si>
+  <si>
     <t xml:space="preserve">945</t>
   </si>
   <si>
+    <t xml:space="preserve">Béliers reproducteurs</t>
+  </si>
+  <si>
     <t xml:space="preserve">949</t>
   </si>
   <si>
+    <t xml:space="preserve">Autres ovins</t>
+  </si>
+  <si>
     <t xml:space="preserve">LGOATBRE</t>
   </si>
   <si>
     <t xml:space="preserve">951</t>
   </si>
   <si>
+    <t xml:space="preserve">Chèvres</t>
+  </si>
+  <si>
     <t xml:space="preserve">LGOATOTH</t>
   </si>
   <si>
     <t xml:space="preserve">952</t>
   </si>
   <si>
+    <t xml:space="preserve">Autres caprins</t>
+  </si>
+  <si>
     <t xml:space="preserve">953</t>
   </si>
   <si>
+    <t xml:space="preserve">Chevrettes</t>
+  </si>
+  <si>
     <t xml:space="preserve">LPIGLET</t>
   </si>
   <si>
     <t xml:space="preserve">961</t>
   </si>
   <si>
+    <t xml:space="preserve">Porcelets</t>
+  </si>
+  <si>
     <t xml:space="preserve">LSOWBRE</t>
   </si>
   <si>
     <t xml:space="preserve">962</t>
   </si>
   <si>
+    <t xml:space="preserve">Truies mères</t>
+  </si>
+  <si>
     <t xml:space="preserve">LPIGFAT</t>
   </si>
   <si>
     <t xml:space="preserve">963</t>
   </si>
   <si>
+    <t xml:space="preserve">Porcs à l'engrais</t>
+  </si>
+  <si>
     <t xml:space="preserve">LPIGOTH</t>
   </si>
   <si>
     <t xml:space="preserve">964</t>
   </si>
   <si>
+    <t xml:space="preserve">Autres porcs</t>
+  </si>
+  <si>
     <t xml:space="preserve">965</t>
   </si>
   <si>
+    <t xml:space="preserve">Cochettes</t>
+  </si>
+  <si>
     <t xml:space="preserve">LPLTRBROYL</t>
   </si>
   <si>
     <t xml:space="preserve">971</t>
   </si>
   <si>
+    <t xml:space="preserve">Poulets de chair</t>
+  </si>
+  <si>
     <t xml:space="preserve">LHENSLAY</t>
   </si>
   <si>
     <t xml:space="preserve">972</t>
   </si>
   <si>
+    <t xml:space="preserve">Poules pondeuses</t>
+  </si>
+  <si>
     <t xml:space="preserve">973</t>
   </si>
   <si>
+    <t xml:space="preserve">Poulettes démarrées</t>
+  </si>
+  <si>
     <t xml:space="preserve">LPLTROTH</t>
   </si>
   <si>
     <t xml:space="preserve">976</t>
   </si>
   <si>
+    <t xml:space="preserve">Dindes</t>
+  </si>
+  <si>
     <t xml:space="preserve">977</t>
   </si>
   <si>
+    <t xml:space="preserve">Pintades</t>
+  </si>
+  <si>
     <t xml:space="preserve">981</t>
   </si>
   <si>
+    <t xml:space="preserve">Autres volailles</t>
+  </si>
+  <si>
     <t xml:space="preserve">982</t>
   </si>
   <si>
+    <t xml:space="preserve">Autres volailles démarrées</t>
+  </si>
+  <si>
     <t xml:space="preserve">985</t>
   </si>
   <si>
+    <t xml:space="preserve">Oies à rôtir</t>
+  </si>
+  <si>
     <t xml:space="preserve">986</t>
   </si>
   <si>
+    <t xml:space="preserve">Oies grasses</t>
+  </si>
+  <si>
     <t xml:space="preserve">987</t>
   </si>
   <si>
+    <t xml:space="preserve">Canards à rôtir</t>
+  </si>
+  <si>
     <t xml:space="preserve">988</t>
   </si>
   <si>
+    <t xml:space="preserve">Canards prêts à gaver (PAG)</t>
+  </si>
+  <si>
     <t xml:space="preserve">989</t>
   </si>
   <si>
+    <t xml:space="preserve">Canards gras</t>
+  </si>
+  <si>
     <t xml:space="preserve">LRABBRE</t>
   </si>
   <si>
     <t xml:space="preserve">991</t>
   </si>
   <si>
+    <t xml:space="preserve">Lapines mères</t>
+  </si>
+  <si>
     <t xml:space="preserve">LRABOTH</t>
   </si>
   <si>
     <t xml:space="preserve">992</t>
   </si>
   <si>
+    <t xml:space="preserve">Autres lapins</t>
+  </si>
+  <si>
     <t xml:space="preserve">997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Animaux d’aquaculture</t>
   </si>
   <si>
     <t xml:space="preserve">LANIMOTH</t>
@@ -2182,8 +2581,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table5" displayName="Table5" ref="A1:D204" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:D204"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table5" displayName="Table5" ref="A1:D205" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:D205"/>
   <tableColumns count="4">
     <tableColumn id="1" name="FADN_code_letter"/>
     <tableColumn id="2" name="national_code"/>
@@ -3791,10 +4190,10 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D1048576"/>
+  <dimension ref="A1:E1048576"/>
   <sheetFormatPr defaultColWidth="10.453125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>159</v>
       </c>
@@ -3807,133 +4206,172 @@
       <c r="D1" s="1" t="s">
         <v>161</v>
       </c>
+      <c r="E1" s="0" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>20</v>
       </c>
+      <c r="E2" s="0" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>20</v>
       </c>
+      <c r="E3" s="0" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="2" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>20</v>
       </c>
+      <c r="E4" s="0" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>20</v>
       </c>
+      <c r="E5" s="0" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>20</v>
       </c>
+      <c r="E6" s="0" t="s">
+        <v>175</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>20</v>
       </c>
+      <c r="E7" s="0" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="2" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>20</v>
       </c>
+      <c r="E8" s="0" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="E9" s="0" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E10" s="0" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="2" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>20</v>
       </c>
+      <c r="E11" s="0" t="s">
+        <v>186</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>20</v>
       </c>
+      <c r="E12" s="0" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="2" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>20</v>
       </c>
+      <c r="E13" s="0" t="s">
+        <v>191</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>20</v>
@@ -3941,7 +4379,7 @@
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>20</v>
@@ -3949,7 +4387,7 @@
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>20</v>
@@ -3957,7 +4395,7 @@
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>20</v>
@@ -3965,7 +4403,7 @@
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>20</v>
@@ -3973,7 +4411,7 @@
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>20</v>
@@ -3981,7 +4419,7 @@
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>20</v>
@@ -3989,7 +4427,7 @@
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>20</v>
@@ -3997,7 +4435,7 @@
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>20</v>
@@ -4005,7 +4443,7 @@
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>20</v>
@@ -4013,7 +4451,7 @@
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>20</v>
@@ -4021,7 +4459,7 @@
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>20</v>
@@ -4029,626 +4467,794 @@
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E26" s="0" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E27" s="0" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E28" s="0" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>199</v>
+        <v>214</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E29" s="0" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>200</v>
+        <v>216</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E30" s="0" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E31" s="0" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E32" s="0" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
-        <v>205</v>
+        <v>224</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>206</v>
+        <v>225</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E33" s="0" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>208</v>
+        <v>228</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E34" s="0" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>209</v>
+        <v>230</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E35" s="0" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2" t="s">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>210</v>
+        <v>232</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E36" s="0" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2" t="s">
-        <v>211</v>
+        <v>234</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>212</v>
+        <v>235</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E37" s="0" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
-        <v>213</v>
+        <v>237</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>212</v>
+        <v>235</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E38" s="0" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2" t="s">
-        <v>211</v>
+        <v>234</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>214</v>
+        <v>238</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E39" s="0" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
-        <v>213</v>
+        <v>237</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>214</v>
+        <v>238</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E40" s="0" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2" t="s">
-        <v>211</v>
+        <v>234</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>215</v>
+        <v>240</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E41" s="0" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
-        <v>213</v>
+        <v>237</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>215</v>
+        <v>240</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E42" s="0" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
-        <v>216</v>
+        <v>242</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>217</v>
+        <v>243</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E43" s="0" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>218</v>
+        <v>245</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>219</v>
+        <v>246</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E44" s="0" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>220</v>
+        <v>248</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>219</v>
+        <v>246</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E45" s="0" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>221</v>
+        <v>249</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>222</v>
+        <v>250</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E46" s="0" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>223</v>
+        <v>252</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>222</v>
+        <v>250</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E47" s="0" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
-        <v>221</v>
+        <v>249</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>224</v>
+        <v>253</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E48" s="0" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2" t="s">
-        <v>223</v>
+        <v>252</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>224</v>
+        <v>253</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E49" s="0" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2" t="s">
-        <v>221</v>
+        <v>249</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>225</v>
+        <v>255</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E50" s="0" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>225</v>
+        <v>255</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E51" s="0" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2" t="s">
-        <v>221</v>
+        <v>249</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>227</v>
+        <v>258</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E52" s="0" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="2" t="s">
-        <v>223</v>
+        <v>252</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>227</v>
+        <v>258</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E53" s="0" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2" t="s">
-        <v>221</v>
+        <v>249</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>228</v>
+        <v>260</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E54" s="0" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="2" t="s">
-        <v>223</v>
+        <v>252</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>228</v>
+        <v>260</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E55" s="0" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
-        <v>221</v>
+        <v>249</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>229</v>
+        <v>262</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E56" s="0" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>229</v>
+        <v>262</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E57" s="0" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="2" t="s">
-        <v>230</v>
+        <v>264</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>231</v>
+        <v>265</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E58" s="0" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="2" t="s">
-        <v>221</v>
+        <v>249</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>231</v>
+        <v>265</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E59" s="0" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="2" t="s">
-        <v>232</v>
+        <v>267</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>233</v>
+        <v>268</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E60" s="0" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="2" t="s">
-        <v>234</v>
+        <v>270</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>235</v>
+        <v>271</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E61" s="0" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="2" t="s">
-        <v>236</v>
+        <v>273</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>237</v>
+        <v>274</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E62" s="0" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="2" t="s">
-        <v>238</v>
+        <v>276</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>239</v>
+        <v>277</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E63" s="0" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="2" t="s">
-        <v>240</v>
+        <v>279</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>241</v>
+        <v>280</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E64" s="0" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="2" t="s">
-        <v>242</v>
+        <v>282</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>243</v>
+        <v>283</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E65" s="0" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="2" t="s">
-        <v>244</v>
+        <v>285</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>245</v>
+        <v>286</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E66" s="0" t="s">
+        <v>287</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="2" t="s">
-        <v>246</v>
+        <v>288</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>247</v>
+        <v>289</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E67" s="0" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="2" t="s">
-        <v>248</v>
+        <v>291</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>249</v>
+        <v>292</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E68" s="0" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="2" t="s">
-        <v>250</v>
+        <v>294</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>251</v>
+        <v>295</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E69" s="0" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="2" t="s">
-        <v>252</v>
+        <v>297</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>253</v>
+        <v>298</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E70" s="0" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="2" t="s">
-        <v>254</v>
+        <v>300</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>255</v>
+        <v>301</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E71" s="0" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="2" t="s">
-        <v>256</v>
+        <v>303</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>255</v>
+        <v>301</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E72" s="0" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="2" t="s">
-        <v>257</v>
+        <v>304</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>255</v>
+        <v>301</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E73" s="0" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="2" t="s">
-        <v>258</v>
+        <v>305</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>259</v>
+        <v>306</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E74" s="0" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="2" t="s">
-        <v>260</v>
+        <v>308</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>259</v>
+        <v>306</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E75" s="0" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="2" t="s">
-        <v>261</v>
+        <v>309</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>262</v>
+        <v>310</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E76" s="0" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="2" t="s">
-        <v>263</v>
+        <v>312</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>264</v>
+        <v>313</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E77" s="0" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="2" t="s">
-        <v>258</v>
+        <v>305</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>265</v>
+        <v>315</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E78" s="0" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="2" t="s">
-        <v>266</v>
+        <v>317</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>267</v>
+        <v>318</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E79" s="0" t="s">
+        <v>319</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="2" t="s">
-        <v>268</v>
+        <v>320</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>269</v>
+        <v>321</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E80" s="0" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="2" t="s">
-        <v>270</v>
+        <v>323</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>271</v>
+        <v>324</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E81" s="0" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="2" t="s">
-        <v>272</v>
+        <v>326</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>273</v>
+        <v>327</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>65</v>
@@ -4656,194 +5262,245 @@
     </row>
     <row r="83" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="2" t="s">
-        <v>274</v>
+        <v>328</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>275</v>
+        <v>329</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E83" s="0" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="2" t="s">
-        <v>276</v>
+        <v>331</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>277</v>
+        <v>332</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E84" s="0" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="2" t="s">
-        <v>278</v>
+        <v>334</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>277</v>
+        <v>332</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E85" s="0" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="2" t="s">
-        <v>279</v>
+        <v>335</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>277</v>
+        <v>332</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E86" s="0" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="2" t="s">
-        <v>280</v>
+        <v>336</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>277</v>
+        <v>332</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E87" s="0" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="2" t="s">
-        <v>281</v>
+        <v>337</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>277</v>
+        <v>332</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E88" s="0" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="2" t="s">
-        <v>282</v>
+        <v>338</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>277</v>
+        <v>332</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E89" s="0" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="2" t="s">
-        <v>283</v>
+        <v>339</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>277</v>
+        <v>332</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E90" s="0" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="2" t="s">
-        <v>284</v>
+        <v>340</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>277</v>
+        <v>332</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E91" s="0" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="2" t="s">
-        <v>285</v>
+        <v>341</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>277</v>
+        <v>332</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E92" s="0" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="2" t="s">
-        <v>286</v>
+        <v>342</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>277</v>
+        <v>332</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E93" s="0" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="2" t="s">
-        <v>287</v>
+        <v>343</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>277</v>
+        <v>332</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E94" s="0" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="2" t="s">
-        <v>288</v>
+        <v>344</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>277</v>
+        <v>332</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E95" s="0" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="2" t="s">
-        <v>289</v>
+        <v>345</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>277</v>
+        <v>332</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E96" s="0" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="2" t="s">
-        <v>290</v>
+        <v>346</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>291</v>
+        <v>347</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E97" s="0" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="2" t="s">
-        <v>290</v>
+        <v>346</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>292</v>
+        <v>349</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E98" s="0" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="2" t="s">
-        <v>293</v>
+        <v>351</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>294</v>
+        <v>352</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E99" s="0" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B100" s="2" t="s">
-        <v>295</v>
+        <v>354</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>65</v>
@@ -4851,76 +5508,94 @@
     </row>
     <row r="101" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="2" t="s">
-        <v>296</v>
+        <v>355</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>297</v>
+        <v>356</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E101" s="0" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="2" t="s">
-        <v>298</v>
+        <v>358</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>299</v>
+        <v>359</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E102" s="0" t="s">
+        <v>360</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="2" t="s">
-        <v>298</v>
+        <v>358</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>300</v>
+        <v>361</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E103" s="0" t="s">
+        <v>362</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="2" t="s">
-        <v>298</v>
+        <v>358</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>301</v>
+        <v>363</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E104" s="0" t="s">
+        <v>364</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="2" t="s">
-        <v>298</v>
+        <v>358</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>302</v>
+        <v>365</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E105" s="0" t="s">
+        <v>366</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="2" t="s">
-        <v>303</v>
+        <v>367</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>304</v>
+        <v>368</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E106" s="0" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="2" t="s">
-        <v>303</v>
+        <v>367</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>305</v>
+        <v>370</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>65</v>
@@ -4928,10 +5603,10 @@
     </row>
     <row r="108" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="2" t="s">
-        <v>303</v>
+        <v>367</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>306</v>
+        <v>371</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>65</v>
@@ -4939,392 +5614,497 @@
     </row>
     <row r="109" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="2" t="s">
-        <v>307</v>
+        <v>372</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>308</v>
+        <v>373</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E109" s="0" t="s">
+        <v>374</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="2" t="s">
-        <v>307</v>
+        <v>372</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>309</v>
+        <v>375</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E110" s="0" t="s">
+        <v>376</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="2" t="s">
-        <v>310</v>
+        <v>377</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>311</v>
+        <v>378</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E111" s="0" t="s">
+        <v>379</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="2" t="s">
-        <v>307</v>
+        <v>372</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>312</v>
+        <v>380</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E112" s="0" t="s">
+        <v>381</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="2" t="s">
-        <v>307</v>
+        <v>372</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>313</v>
+        <v>382</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E113" s="0" t="s">
+        <v>383</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="2" t="s">
-        <v>307</v>
+        <v>372</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>314</v>
+        <v>384</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E114" s="0" t="s">
+        <v>385</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="2" t="s">
-        <v>315</v>
+        <v>386</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>316</v>
+        <v>387</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E115" s="0" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="2" t="s">
-        <v>317</v>
+        <v>389</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>318</v>
+        <v>390</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E116" s="0" t="s">
+        <v>391</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="2" t="s">
-        <v>319</v>
+        <v>392</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>320</v>
+        <v>393</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E117" s="0" t="s">
+        <v>394</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="2" t="s">
-        <v>321</v>
+        <v>395</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>322</v>
+        <v>396</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E118" s="0" t="s">
+        <v>397</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="2" t="s">
-        <v>323</v>
+        <v>398</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>324</v>
+        <v>399</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E119" s="0" t="s">
+        <v>400</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="2" t="s">
-        <v>325</v>
+        <v>401</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>326</v>
+        <v>402</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E120" s="0" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="2" t="s">
-        <v>327</v>
+        <v>404</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>326</v>
+        <v>402</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E121" s="0" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="2" t="s">
-        <v>328</v>
+        <v>405</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>326</v>
+        <v>402</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E122" s="0" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="2" t="s">
-        <v>329</v>
+        <v>406</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>330</v>
+        <v>407</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E123" s="0" t="s">
+        <v>408</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="2" t="s">
-        <v>329</v>
+        <v>406</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>331</v>
+        <v>409</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E124" s="0" t="s">
+        <v>410</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="2" t="s">
-        <v>332</v>
+        <v>411</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>331</v>
+        <v>409</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E125" s="0" t="s">
+        <v>408</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="2" t="s">
-        <v>333</v>
+        <v>412</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>334</v>
+        <v>413</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E126" s="0" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="2" t="s">
-        <v>335</v>
+        <v>415</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>334</v>
+        <v>413</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E127" s="0" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="2" t="s">
-        <v>336</v>
+        <v>416</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>334</v>
+        <v>413</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E128" s="0" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="2" t="s">
-        <v>333</v>
+        <v>412</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>337</v>
+        <v>417</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E129" s="0" t="s">
+        <v>418</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="2" t="s">
-        <v>336</v>
+        <v>416</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>337</v>
+        <v>417</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E130" s="0" t="s">
+        <v>418</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="2" t="s">
-        <v>338</v>
+        <v>419</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>339</v>
+        <v>420</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E131" s="0" t="s">
+        <v>421</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="2" t="s">
-        <v>335</v>
+        <v>415</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>339</v>
+        <v>420</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E132" s="0" t="s">
+        <v>421</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="2" t="s">
-        <v>340</v>
+        <v>422</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>339</v>
+        <v>420</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E133" s="0" t="s">
+        <v>421</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="2" t="s">
-        <v>338</v>
+        <v>419</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>341</v>
+        <v>423</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E134" s="0" t="s">
+        <v>424</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="2" t="s">
-        <v>340</v>
+        <v>422</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>341</v>
+        <v>423</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E135" s="0" t="s">
+        <v>424</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="2" t="s">
-        <v>342</v>
+        <v>425</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>343</v>
+        <v>426</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E136" s="0" t="s">
+        <v>427</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="2" t="s">
-        <v>335</v>
+        <v>415</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>343</v>
+        <v>426</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E137" s="0" t="s">
+        <v>427</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="2" t="s">
-        <v>344</v>
+        <v>428</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>343</v>
+        <v>426</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E138" s="0" t="s">
+        <v>427</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="2" t="s">
-        <v>342</v>
+        <v>425</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>345</v>
+        <v>429</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E139" s="0" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="2" t="s">
-        <v>344</v>
+        <v>428</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>345</v>
+        <v>429</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E140" s="0" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="2" t="s">
-        <v>346</v>
+        <v>431</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>347</v>
+        <v>432</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E141" s="0" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="2" t="s">
-        <v>348</v>
+        <v>434</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>349</v>
+        <v>435</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E142" s="0" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="2" t="s">
-        <v>350</v>
+        <v>437</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>351</v>
+        <v>438</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E143" s="0" t="s">
+        <v>439</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="2" t="s">
-        <v>352</v>
+        <v>440</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>65</v>
@@ -5332,485 +6112,620 @@
     </row>
     <row r="145" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="2" t="s">
-        <v>353</v>
+        <v>441</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>354</v>
+        <v>442</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>100</v>
+      </c>
+      <c r="E145" s="0" t="s">
+        <v>443</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="2" t="s">
-        <v>353</v>
+        <v>441</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>355</v>
+        <v>444</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>100</v>
+      </c>
+      <c r="E146" s="0" t="s">
+        <v>445</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="2" t="s">
-        <v>356</v>
+        <v>446</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>357</v>
+        <v>447</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>100</v>
+      </c>
+      <c r="E147" s="0" t="s">
+        <v>448</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="2" t="s">
-        <v>356</v>
+        <v>446</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>358</v>
+        <v>449</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>100</v>
+      </c>
+      <c r="E148" s="0" t="s">
+        <v>450</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="2" t="s">
-        <v>359</v>
+        <v>451</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>360</v>
+        <v>452</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>100</v>
+      </c>
+      <c r="E149" s="0" t="s">
+        <v>453</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="2" t="s">
-        <v>361</v>
+        <v>454</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>362</v>
+        <v>455</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>100</v>
+      </c>
+      <c r="E150" s="0" t="s">
+        <v>456</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="2" t="s">
-        <v>363</v>
+        <v>457</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>364</v>
+        <v>458</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>100</v>
+      </c>
+      <c r="E151" s="0" t="s">
+        <v>459</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="2" t="s">
-        <v>365</v>
+        <v>460</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>366</v>
+        <v>461</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>100</v>
+      </c>
+      <c r="E152" s="0" t="s">
+        <v>462</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="2" t="s">
-        <v>367</v>
+        <v>463</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>368</v>
+        <v>464</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>100</v>
+      </c>
+      <c r="E153" s="0" t="s">
+        <v>465</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="2" t="s">
-        <v>356</v>
+        <v>446</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>369</v>
+        <v>466</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>100</v>
+      </c>
+      <c r="E154" s="0" t="s">
+        <v>467</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="2" t="s">
-        <v>356</v>
+        <v>446</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>370</v>
+        <v>468</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>100</v>
+      </c>
+      <c r="E155" s="0" t="s">
+        <v>469</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="2" t="s">
-        <v>371</v>
+        <v>446</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>372</v>
+        <v>470</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>100</v>
+      </c>
+      <c r="E156" s="0" t="s">
+        <v>471</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="2" t="s">
-        <v>371</v>
+        <v>472</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>373</v>
+        <v>473</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>100</v>
+      </c>
+      <c r="E157" s="0" t="s">
+        <v>474</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="2" t="s">
-        <v>374</v>
+        <v>472</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>375</v>
+        <v>475</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>100</v>
+      </c>
+      <c r="E158" s="0" t="s">
+        <v>476</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="2" t="s">
-        <v>374</v>
+        <v>477</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>376</v>
+        <v>478</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>100</v>
+      </c>
+      <c r="E159" s="0" t="s">
+        <v>479</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="2" t="s">
-        <v>377</v>
+        <v>477</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>378</v>
+        <v>480</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>100</v>
+      </c>
+      <c r="E160" s="0" t="s">
+        <v>481</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="2" t="s">
-        <v>377</v>
+        <v>482</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>379</v>
+        <v>483</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>100</v>
+      </c>
+      <c r="E161" s="0" t="s">
+        <v>484</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="2" t="s">
-        <v>380</v>
+        <v>482</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>381</v>
+        <v>485</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>100</v>
+      </c>
+      <c r="E162" s="0" t="s">
+        <v>486</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="2" t="s">
-        <v>380</v>
+        <v>487</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>382</v>
+        <v>488</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>100</v>
+      </c>
+      <c r="E163" s="0" t="s">
+        <v>489</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="2" t="s">
-        <v>380</v>
+        <v>487</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>383</v>
+        <v>490</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>100</v>
+      </c>
+      <c r="E164" s="0" t="s">
+        <v>491</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="2" t="s">
-        <v>384</v>
+        <v>487</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>385</v>
+        <v>492</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>100</v>
+      </c>
+      <c r="E165" s="0" t="s">
+        <v>493</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="2" t="s">
-        <v>386</v>
+        <v>494</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>387</v>
+        <v>495</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>100</v>
+      </c>
+      <c r="E166" s="0" t="s">
+        <v>496</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="2" t="s">
-        <v>386</v>
+        <v>497</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>388</v>
+        <v>498</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>100</v>
+      </c>
+      <c r="E167" s="0" t="s">
+        <v>499</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="2" t="s">
-        <v>389</v>
+        <v>497</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>390</v>
+        <v>500</v>
       </c>
       <c r="C168" s="2" t="s">
         <v>100</v>
+      </c>
+      <c r="E168" s="0" t="s">
+        <v>501</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="2" t="s">
-        <v>391</v>
+        <v>502</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>392</v>
+        <v>503</v>
       </c>
       <c r="C169" s="2" t="s">
         <v>100</v>
+      </c>
+      <c r="E169" s="0" t="s">
+        <v>504</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="2" t="s">
-        <v>393</v>
+        <v>505</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>394</v>
+        <v>506</v>
       </c>
       <c r="C170" s="2" t="s">
         <v>100</v>
+      </c>
+      <c r="E170" s="0" t="s">
+        <v>507</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="2" t="s">
-        <v>395</v>
+        <v>508</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>396</v>
+        <v>509</v>
       </c>
       <c r="C171" s="2" t="s">
         <v>100</v>
+      </c>
+      <c r="E171" s="0" t="s">
+        <v>510</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="2" t="s">
-        <v>395</v>
+        <v>511</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>397</v>
+        <v>512</v>
       </c>
       <c r="C172" s="2" t="s">
         <v>100</v>
+      </c>
+      <c r="E172" s="0" t="s">
+        <v>513</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="2" t="s">
-        <v>398</v>
+        <v>511</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>399</v>
+        <v>514</v>
       </c>
       <c r="C173" s="2" t="s">
         <v>100</v>
+      </c>
+      <c r="E173" s="0" t="s">
+        <v>515</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="2" t="s">
-        <v>400</v>
+        <v>516</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>401</v>
+        <v>517</v>
       </c>
       <c r="C174" s="2" t="s">
         <v>100</v>
+      </c>
+      <c r="E174" s="0" t="s">
+        <v>518</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="2" t="s">
-        <v>400</v>
+        <v>519</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>402</v>
+        <v>520</v>
       </c>
       <c r="C175" s="2" t="s">
         <v>100</v>
+      </c>
+      <c r="E175" s="0" t="s">
+        <v>521</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="2" t="s">
-        <v>403</v>
+        <v>519</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>404</v>
+        <v>522</v>
       </c>
       <c r="C176" s="2" t="s">
         <v>100</v>
+      </c>
+      <c r="E176" s="0" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="2" t="s">
-        <v>403</v>
+        <v>524</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>405</v>
+        <v>525</v>
       </c>
       <c r="C177" s="2" t="s">
         <v>100</v>
+      </c>
+      <c r="E177" s="0" t="s">
+        <v>526</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="2" t="s">
-        <v>403</v>
+        <v>524</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>406</v>
+        <v>527</v>
       </c>
       <c r="C178" s="2" t="s">
         <v>100</v>
+      </c>
+      <c r="E178" s="0" t="s">
+        <v>528</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="2" t="s">
-        <v>403</v>
+        <v>524</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>407</v>
+        <v>529</v>
       </c>
       <c r="C179" s="2" t="s">
         <v>100</v>
+      </c>
+      <c r="E179" s="0" t="s">
+        <v>530</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="2" t="s">
-        <v>403</v>
+        <v>524</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>408</v>
+        <v>531</v>
       </c>
       <c r="C180" s="2" t="s">
         <v>100</v>
+      </c>
+      <c r="E180" s="0" t="s">
+        <v>532</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="2" t="s">
-        <v>403</v>
+        <v>524</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>409</v>
+        <v>533</v>
       </c>
       <c r="C181" s="2" t="s">
         <v>100</v>
+      </c>
+      <c r="E181" s="0" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="2" t="s">
-        <v>403</v>
+        <v>524</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>410</v>
+        <v>535</v>
       </c>
       <c r="C182" s="2" t="s">
         <v>100</v>
+      </c>
+      <c r="E182" s="0" t="s">
+        <v>536</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="2" t="s">
-        <v>403</v>
+        <v>524</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>411</v>
+        <v>537</v>
       </c>
       <c r="C183" s="2" t="s">
         <v>100</v>
+      </c>
+      <c r="E183" s="0" t="s">
+        <v>538</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="2" t="s">
-        <v>403</v>
+        <v>524</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>412</v>
+        <v>539</v>
       </c>
       <c r="C184" s="2" t="s">
         <v>100</v>
+      </c>
+      <c r="E184" s="0" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="2" t="s">
-        <v>413</v>
+        <v>524</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>414</v>
+        <v>541</v>
       </c>
       <c r="C185" s="2" t="s">
         <v>100</v>
+      </c>
+      <c r="E185" s="0" t="s">
+        <v>542</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="2" t="s">
-        <v>415</v>
+        <v>543</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>416</v>
+        <v>544</v>
       </c>
       <c r="C186" s="2" t="s">
         <v>100</v>
       </c>
+      <c r="E186" s="0" t="s">
+        <v>545</v>
+      </c>
     </row>
     <row r="187" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A187" s="2" t="s">
+        <v>546</v>
+      </c>
       <c r="B187" s="2" t="s">
-        <v>417</v>
+        <v>547</v>
       </c>
       <c r="C187" s="2" t="s">
         <v>100</v>
       </c>
+      <c r="E187" s="0" t="s">
+        <v>548</v>
+      </c>
     </row>
     <row r="188" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A188" s="2" t="s">
-        <v>418</v>
+      <c r="B188" s="2" t="s">
+        <v>549</v>
       </c>
       <c r="C188" s="2" t="s">
         <v>100</v>
+      </c>
+      <c r="E188" s="0" t="s">
+        <v>550</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="2" t="s">
-        <v>419</v>
+        <v>551</v>
       </c>
       <c r="C189" s="2" t="s">
         <v>100</v>
@@ -5818,7 +6733,7 @@
     </row>
     <row r="190" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="2" t="s">
-        <v>420</v>
+        <v>552</v>
       </c>
       <c r="C190" s="2" t="s">
         <v>100</v>
@@ -5826,7 +6741,7 @@
     </row>
     <row r="191" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="2" t="s">
-        <v>421</v>
+        <v>553</v>
       </c>
       <c r="C191" s="2" t="s">
         <v>100</v>
@@ -5834,7 +6749,7 @@
     </row>
     <row r="192" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="2" t="s">
-        <v>422</v>
+        <v>554</v>
       </c>
       <c r="C192" s="2" t="s">
         <v>100</v>
@@ -5842,7 +6757,7 @@
     </row>
     <row r="193" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="2" t="s">
-        <v>423</v>
+        <v>555</v>
       </c>
       <c r="C193" s="2" t="s">
         <v>100</v>
@@ -5850,7 +6765,7 @@
     </row>
     <row r="194" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="2" t="s">
-        <v>424</v>
+        <v>556</v>
       </c>
       <c r="C194" s="2" t="s">
         <v>100</v>
@@ -5858,7 +6773,7 @@
     </row>
     <row r="195" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="2" t="s">
-        <v>425</v>
+        <v>557</v>
       </c>
       <c r="C195" s="2" t="s">
         <v>100</v>
@@ -5866,7 +6781,7 @@
     </row>
     <row r="196" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="2" t="s">
-        <v>426</v>
+        <v>558</v>
       </c>
       <c r="C196" s="2" t="s">
         <v>100</v>
@@ -5874,7 +6789,7 @@
     </row>
     <row r="197" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="2" t="s">
-        <v>427</v>
+        <v>559</v>
       </c>
       <c r="C197" s="2" t="s">
         <v>100</v>
@@ -5882,7 +6797,7 @@
     </row>
     <row r="198" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="2" t="s">
-        <v>428</v>
+        <v>560</v>
       </c>
       <c r="C198" s="2" t="s">
         <v>100</v>
@@ -5890,7 +6805,7 @@
     </row>
     <row r="199" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="2" t="s">
-        <v>429</v>
+        <v>561</v>
       </c>
       <c r="C199" s="2" t="s">
         <v>100</v>
@@ -5898,7 +6813,7 @@
     </row>
     <row r="200" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="2" t="s">
-        <v>430</v>
+        <v>562</v>
       </c>
       <c r="C200" s="2" t="s">
         <v>100</v>
@@ -5906,7 +6821,7 @@
     </row>
     <row r="201" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="2" t="s">
-        <v>431</v>
+        <v>563</v>
       </c>
       <c r="C201" s="2" t="s">
         <v>100</v>
@@ -5914,7 +6829,7 @@
     </row>
     <row r="202" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="2" t="s">
-        <v>432</v>
+        <v>564</v>
       </c>
       <c r="C202" s="2" t="s">
         <v>100</v>
@@ -5922,7 +6837,7 @@
     </row>
     <row r="203" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="2" t="s">
-        <v>433</v>
+        <v>565</v>
       </c>
       <c r="C203" s="2" t="s">
         <v>100</v>
@@ -5930,13 +6845,20 @@
     </row>
     <row r="204" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="2" t="s">
-        <v>434</v>
+        <v>566</v>
       </c>
       <c r="C204" s="2" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="205" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A205" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="C205" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
     <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -5967,7 +6889,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>435</v>
+        <v>568</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>9</v>
@@ -5976,7 +6898,7 @@
         <v>10</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>436</v>
+        <v>569</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>13</v>
@@ -5985,10 +6907,10 @@
         <v>14</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>437</v>
+        <v>570</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>438</v>
+        <v>571</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>15</v>
@@ -5997,54 +6919,54 @@
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>439</v>
+        <v>572</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>440</v>
+        <v>573</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>441</v>
+        <v>574</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>442</v>
+        <v>575</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>443</v>
+        <v>576</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2" t="s">
-        <v>444</v>
+        <v>577</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>445</v>
+        <v>578</v>
       </c>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>446</v>
+        <v>579</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>447</v>
+        <v>580</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>448</v>
+        <v>581</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>449</v>
+        <v>582</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>450</v>
+        <v>583</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>43</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>451</v>
+        <v>584</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>445</v>
+        <v>578</v>
       </c>
       <c r="I3" s="2" t="n">
         <v>1</v>
@@ -6053,28 +6975,28 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>452</v>
+        <v>585</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>453</v>
+        <v>586</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>448</v>
+        <v>581</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>454</v>
+        <v>587</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>455</v>
+        <v>588</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>43</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>451</v>
+        <v>584</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>445</v>
+        <v>578</v>
       </c>
       <c r="I4" s="2" t="n">
         <v>1</v>
@@ -6083,28 +7005,28 @@
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>446</v>
+        <v>579</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>447</v>
+        <v>580</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>448</v>
+        <v>581</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>456</v>
+        <v>589</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>457</v>
+        <v>590</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>43</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>451</v>
+        <v>584</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>445</v>
+        <v>578</v>
       </c>
       <c r="I5" s="2" t="n">
         <v>1</v>
@@ -6113,28 +7035,28 @@
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>452</v>
+        <v>585</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>453</v>
+        <v>586</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>448</v>
+        <v>581</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>458</v>
+        <v>591</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>459</v>
+        <v>592</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>43</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>451</v>
+        <v>584</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>445</v>
+        <v>578</v>
       </c>
       <c r="I6" s="2" t="n">
         <v>1</v>
@@ -6143,75 +7065,75 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>460</v>
+        <v>593</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>461</v>
+        <v>594</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>462</v>
+        <v>595</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>463</v>
+        <v>596</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>464</v>
+        <v>597</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2" t="s">
-        <v>444</v>
+        <v>577</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>445</v>
+        <v>578</v>
       </c>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>465</v>
+        <v>598</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>466</v>
+        <v>599</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>467</v>
+        <v>600</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>468</v>
+        <v>601</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>469</v>
+        <v>602</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2" t="s">
-        <v>444</v>
+        <v>577</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>445</v>
+        <v>578</v>
       </c>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>470</v>
+        <v>603</v>
       </c>
       <c r="B9" s="2"/>
       <c r="D9" s="3" t="s">
-        <v>471</v>
+        <v>604</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>472</v>
+        <v>605</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>473</v>
+        <v>606</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>474</v>
+        <v>607</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>445</v>
+        <v>578</v>
       </c>
       <c r="I9" s="2" t="n">
         <v>1</v>
@@ -6220,28 +7142,28 @@
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>475</v>
+        <v>608</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>476</v>
+        <v>609</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>448</v>
+        <v>581</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>477</v>
+        <v>610</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>478</v>
+        <v>611</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>43</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>451</v>
+        <v>584</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>445</v>
+        <v>578</v>
       </c>
       <c r="I10" s="2" t="n">
         <v>1</v>
@@ -6250,23 +7172,23 @@
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>479</v>
+        <v>612</v>
       </c>
       <c r="B11" s="2"/>
       <c r="D11" s="2" t="s">
-        <v>480</v>
+        <v>613</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>481</v>
+        <v>614</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>473</v>
+        <v>606</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>474</v>
+        <v>607</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>445</v>
+        <v>578</v>
       </c>
       <c r="I11" s="2" t="n">
         <v>1</v>
@@ -6275,28 +7197,28 @@
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>482</v>
+        <v>615</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>483</v>
+        <v>616</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>448</v>
+        <v>581</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>484</v>
+        <v>617</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>485</v>
+        <v>618</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>43</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>451</v>
+        <v>584</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>445</v>
+        <v>578</v>
       </c>
       <c r="I12" s="2" t="n">
         <v>1</v>
@@ -6305,28 +7227,28 @@
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>486</v>
+        <v>619</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>487</v>
+        <v>620</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>448</v>
+        <v>581</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>488</v>
+        <v>621</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>489</v>
+        <v>622</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>43</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>451</v>
+        <v>584</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>445</v>
+        <v>578</v>
       </c>
       <c r="I13" s="2" t="n">
         <v>1</v>
@@ -6335,28 +7257,28 @@
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>490</v>
+        <v>623</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>491</v>
+        <v>624</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>492</v>
+        <v>625</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>493</v>
+        <v>626</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>494</v>
+        <v>627</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>495</v>
+        <v>628</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>451</v>
+        <v>584</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>445</v>
+        <v>578</v>
       </c>
       <c r="I14" s="2" t="n">
         <v>0.001</v>
@@ -6365,28 +7287,28 @@
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>496</v>
+        <v>629</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>497</v>
+        <v>630</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>492</v>
+        <v>625</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>498</v>
+        <v>631</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>499</v>
+        <v>632</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>495</v>
+        <v>628</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>451</v>
+        <v>584</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>445</v>
+        <v>578</v>
       </c>
       <c r="I15" s="2" t="n">
         <v>0.001</v>
@@ -6395,28 +7317,28 @@
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>500</v>
+        <v>633</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>501</v>
+        <v>634</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>492</v>
+        <v>625</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>502</v>
+        <v>635</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>503</v>
+        <v>636</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>495</v>
+        <v>628</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>451</v>
+        <v>584</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>445</v>
+        <v>578</v>
       </c>
       <c r="I16" s="2" t="n">
         <v>0.001</v>
@@ -6425,28 +7347,28 @@
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>504</v>
+        <v>637</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>505</v>
+        <v>638</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>448</v>
+        <v>581</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>506</v>
+        <v>639</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>507</v>
+        <v>640</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>43</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>451</v>
+        <v>584</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>445</v>
+        <v>578</v>
       </c>
       <c r="I17" s="2" t="n">
         <v>1</v>
@@ -6455,23 +7377,23 @@
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>508</v>
+        <v>641</v>
       </c>
       <c r="B18" s="2"/>
       <c r="D18" s="2" t="s">
-        <v>509</v>
+        <v>642</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>510</v>
+        <v>643</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>511</v>
+        <v>644</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>474</v>
+        <v>607</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>445</v>
+        <v>578</v>
       </c>
       <c r="I18" s="2" t="n">
         <v>1</v>
@@ -6480,26 +7402,26 @@
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>512</v>
+        <v>645</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>513</v>
+        <v>646</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>514</v>
+        <v>647</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>515</v>
+        <v>648</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>516</v>
+        <v>649</v>
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="2" t="s">
-        <v>517</v>
+        <v>650</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>445</v>
+        <v>578</v>
       </c>
       <c r="I19" s="2" t="n">
         <v>1</v>
@@ -6508,52 +7430,52 @@
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>518</v>
+        <v>651</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>519</v>
+        <v>652</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>520</v>
+        <v>653</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>521</v>
+        <v>654</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>522</v>
+        <v>655</v>
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="2" t="s">
-        <v>517</v>
+        <v>650</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>445</v>
+        <v>578</v>
       </c>
       <c r="I20" s="2"/>
       <c r="J20" s="1"/>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>523</v>
+        <v>656</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>524</v>
+        <v>657</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>525</v>
+        <v>658</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>526</v>
+        <v>659</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>527</v>
+        <v>660</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2" t="s">
-        <v>528</v>
+        <v>661</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>445</v>
+        <v>578</v>
       </c>
       <c r="I21" s="2" t="n">
         <v>1</v>
@@ -6562,204 +7484,204 @@
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>529</v>
+        <v>662</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>530</v>
+        <v>663</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>462</v>
+        <v>595</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>531</v>
+        <v>664</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>532</v>
+        <v>665</v>
       </c>
       <c r="F22" s="2"/>
       <c r="G22" s="2" t="s">
-        <v>444</v>
+        <v>577</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>445</v>
+        <v>578</v>
       </c>
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
     </row>
     <row r="23" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>533</v>
+        <v>666</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>534</v>
+        <v>667</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>535</v>
+        <v>668</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>536</v>
+        <v>669</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>537</v>
+        <v>670</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2" t="s">
-        <v>528</v>
+        <v>661</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>445</v>
+        <v>578</v>
       </c>
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
     </row>
     <row r="24" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>538</v>
+        <v>671</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>539</v>
+        <v>672</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>540</v>
+        <v>673</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>541</v>
+        <v>674</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>542</v>
+        <v>675</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" s="2" t="s">
-        <v>528</v>
+        <v>661</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>445</v>
+        <v>578</v>
       </c>
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
     </row>
     <row r="25" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>543</v>
+        <v>676</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>544</v>
+        <v>677</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" s="2" t="s">
-        <v>541</v>
+        <v>674</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>542</v>
+        <v>675</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2" t="s">
-        <v>444</v>
+        <v>577</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>445</v>
+        <v>578</v>
       </c>
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
     </row>
     <row r="26" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>545</v>
+        <v>678</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>546</v>
+        <v>679</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" s="3" t="s">
-        <v>547</v>
+        <v>680</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>548</v>
+        <v>681</v>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="2" t="s">
-        <v>444</v>
+        <v>577</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>445</v>
+        <v>578</v>
       </c>
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>549</v>
+        <v>682</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>550</v>
+        <v>683</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" s="3" t="s">
-        <v>551</v>
+        <v>684</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>552</v>
+        <v>685</v>
       </c>
       <c r="F27" s="3"/>
       <c r="G27" s="2" t="s">
-        <v>444</v>
+        <v>577</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>445</v>
+        <v>578</v>
       </c>
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
     </row>
     <row r="28" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>553</v>
+        <v>686</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>554</v>
+        <v>687</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>555</v>
+        <v>688</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>556</v>
+        <v>689</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>557</v>
+        <v>690</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2" t="s">
-        <v>528</v>
+        <v>661</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>445</v>
+        <v>578</v>
       </c>
       <c r="I28" s="2"/>
       <c r="J28" s="2"/>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>558</v>
+        <v>691</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>559</v>
+        <v>692</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>448</v>
+        <v>581</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>560</v>
+        <v>693</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>561</v>
+        <v>694</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>43</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>451</v>
+        <v>584</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>445</v>
+        <v>578</v>
       </c>
       <c r="I29" s="2" t="n">
         <v>1</v>
@@ -6768,54 +7690,54 @@
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>562</v>
+        <v>695</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>563</v>
+        <v>696</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>462</v>
+        <v>595</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>564</v>
+        <v>697</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>565</v>
+        <v>698</v>
       </c>
       <c r="F30" s="2"/>
       <c r="G30" s="2" t="s">
-        <v>444</v>
+        <v>577</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>445</v>
+        <v>578</v>
       </c>
       <c r="I30" s="2"/>
       <c r="J30" s="2"/>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>566</v>
+        <v>699</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>567</v>
+        <v>700</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>568</v>
+        <v>701</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>569</v>
+        <v>702</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>570</v>
+        <v>703</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>75</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>444</v>
+        <v>577</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>445</v>
+        <v>578</v>
       </c>
       <c r="I31" s="2" t="n">
         <v>0.01</v>
@@ -6824,28 +7746,28 @@
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>571</v>
+        <v>704</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>572</v>
+        <v>705</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>573</v>
+        <v>706</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>574</v>
+        <v>707</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>575</v>
+        <v>708</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>75</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>576</v>
+        <v>709</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>445</v>
+        <v>578</v>
       </c>
       <c r="I32" s="2" t="n">
         <v>0.01</v>
@@ -6854,81 +7776,81 @@
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
-        <v>577</v>
+        <v>710</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>578</v>
+        <v>711</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>577</v>
+        <v>710</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>579</v>
+        <v>712</v>
       </c>
       <c r="F33" s="2"/>
       <c r="G33" s="2" t="s">
-        <v>474</v>
+        <v>607</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>445</v>
+        <v>578</v>
       </c>
       <c r="I33" s="2"/>
       <c r="J33" s="2"/>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>580</v>
+        <v>713</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>581</v>
+        <v>714</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>582</v>
+        <v>715</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>583</v>
+        <v>716</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>584</v>
+        <v>717</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>585</v>
+        <v>718</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>576</v>
+        <v>709</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>445</v>
+        <v>578</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="J34" s="2"/>
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
-        <v>586</v>
+        <v>719</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>587</v>
+        <v>720</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>448</v>
+        <v>581</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>588</v>
+        <v>721</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>589</v>
+        <v>722</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>43</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>451</v>
+        <v>584</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>445</v>
+        <v>578</v>
       </c>
       <c r="I35" s="2" t="n">
         <v>1</v>
@@ -6965,13 +7887,13 @@
         <v>12</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>590</v>
+        <v>723</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>591</v>
+        <v>724</v>
       </c>
     </row>
   </sheetData>
@@ -7001,7 +7923,7 @@
         <v>11</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>592</v>
+        <v>725</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7009,7 +7931,7 @@
         <v>65</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>593</v>
+        <v>726</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7017,7 +7939,7 @@
         <v>65</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>594</v>
+        <v>727</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7025,7 +7947,7 @@
         <v>65</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>595</v>
+        <v>728</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7033,7 +7955,7 @@
         <v>65</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>596</v>
+        <v>729</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7041,7 +7963,7 @@
         <v>65</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>597</v>
+        <v>730</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7049,7 +7971,7 @@
         <v>65</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>598</v>
+        <v>731</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7065,7 +7987,7 @@
         <v>65</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>599</v>
+        <v>732</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7073,7 +7995,7 @@
         <v>65</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>600</v>
+        <v>733</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7097,7 +8019,7 @@
         <v>65</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>601</v>
+        <v>734</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7105,7 +8027,7 @@
         <v>65</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>602</v>
+        <v>735</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7113,7 +8035,7 @@
         <v>65</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>603</v>
+        <v>736</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7121,7 +8043,7 @@
         <v>65</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>604</v>
+        <v>737</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7129,7 +8051,7 @@
         <v>65</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>605</v>
+        <v>738</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7169,7 +8091,7 @@
         <v>65</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>606</v>
+        <v>739</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7185,7 +8107,7 @@
         <v>65</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>607</v>
+        <v>740</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7193,7 +8115,7 @@
         <v>65</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>608</v>
+        <v>741</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7217,7 +8139,7 @@
         <v>100</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>609</v>
+        <v>742</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7257,7 +8179,7 @@
         <v>100</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>610</v>
+        <v>743</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7289,7 +8211,7 @@
         <v>100</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>611</v>
+        <v>744</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7305,7 +8227,7 @@
         <v>100</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>612</v>
+        <v>745</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7313,7 +8235,7 @@
         <v>20</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>613</v>
+        <v>746</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7321,7 +8243,7 @@
         <v>20</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>614</v>
+        <v>747</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7329,7 +8251,7 @@
         <v>20</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>615</v>
+        <v>748</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7337,7 +8259,7 @@
         <v>20</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>616</v>
+        <v>749</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7345,7 +8267,7 @@
         <v>20</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>617</v>
+        <v>750</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7353,7 +8275,7 @@
         <v>20</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>618</v>
+        <v>751</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7385,7 +8307,7 @@
         <v>20</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>619</v>
+        <v>752</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7393,7 +8315,7 @@
         <v>20</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>620</v>
+        <v>753</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7401,7 +8323,7 @@
         <v>20</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>621</v>
+        <v>754</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7409,7 +8331,7 @@
         <v>20</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>622</v>
+        <v>755</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7457,7 +8379,7 @@
         <v>20</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>623</v>
+        <v>756</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7465,7 +8387,7 @@
         <v>20</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>624</v>
+        <v>757</v>
       </c>
     </row>
   </sheetData>
@@ -7506,10 +8428,10 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>290</v>
+        <v>346</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>291</v>
+        <v>347</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>65</v>
@@ -7517,10 +8439,10 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>290</v>
+        <v>346</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>292</v>
+        <v>349</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>65</v>
@@ -7528,10 +8450,10 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>272</v>
+        <v>326</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>273</v>
+        <v>327</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>65</v>
@@ -7539,10 +8461,10 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>350</v>
+        <v>437</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>351</v>
+        <v>438</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>65</v>
@@ -7550,10 +8472,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>303</v>
+        <v>367</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>304</v>
+        <v>368</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>65</v>
@@ -7561,10 +8483,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>303</v>
+        <v>367</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>305</v>
+        <v>370</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>65</v>
@@ -7572,10 +8494,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>303</v>
+        <v>367</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>306</v>
+        <v>371</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>65</v>
@@ -7583,10 +8505,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>199</v>
+        <v>214</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>65</v>
@@ -7594,10 +8516,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>200</v>
+        <v>216</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>65</v>
@@ -7605,10 +8527,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>65</v>
@@ -7616,10 +8538,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>209</v>
+        <v>230</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>65</v>
@@ -7627,10 +8549,10 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>210</v>
+        <v>232</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>65</v>
@@ -7638,10 +8560,10 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>276</v>
+        <v>331</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>277</v>
+        <v>332</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>65</v>
@@ -7649,10 +8571,10 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>321</v>
+        <v>395</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>322</v>
+        <v>396</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>65</v>
@@ -7660,10 +8582,10 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>317</v>
+        <v>389</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>318</v>
+        <v>390</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>65</v>
@@ -7671,10 +8593,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>254</v>
+        <v>300</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>255</v>
+        <v>301</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>65</v>
@@ -7682,10 +8604,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>278</v>
+        <v>334</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>277</v>
+        <v>332</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>65</v>
@@ -7693,10 +8615,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>256</v>
+        <v>303</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>255</v>
+        <v>301</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>65</v>
@@ -7704,10 +8626,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>257</v>
+        <v>304</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>255</v>
+        <v>301</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>65</v>
@@ -7715,10 +8637,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>240</v>
+        <v>279</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>241</v>
+        <v>280</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>65</v>
@@ -7726,10 +8648,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>263</v>
+        <v>312</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>264</v>
+        <v>313</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>65</v>
@@ -7737,10 +8659,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>230</v>
+        <v>264</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>231</v>
+        <v>265</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>65</v>
@@ -7748,10 +8670,10 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>279</v>
+        <v>335</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>277</v>
+        <v>332</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>65</v>
@@ -7759,10 +8681,10 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>244</v>
+        <v>285</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>245</v>
+        <v>286</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>65</v>
@@ -7770,10 +8692,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>261</v>
+        <v>309</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>262</v>
+        <v>310</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>65</v>
@@ -7781,10 +8703,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>258</v>
+        <v>305</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>259</v>
+        <v>306</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>65</v>
@@ -7792,10 +8714,10 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>258</v>
+        <v>305</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>265</v>
+        <v>315</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>65</v>
@@ -7803,10 +8725,10 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>260</v>
+        <v>308</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>259</v>
+        <v>306</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>65</v>
@@ -7814,10 +8736,10 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>348</v>
+        <v>434</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>349</v>
+        <v>435</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>65</v>
@@ -7825,10 +8747,10 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>310</v>
+        <v>377</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>311</v>
+        <v>378</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>65</v>
@@ -7836,10 +8758,10 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>307</v>
+        <v>372</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>312</v>
+        <v>380</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>65</v>
@@ -7847,10 +8769,10 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
-        <v>307</v>
+        <v>372</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>313</v>
+        <v>382</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>65</v>
@@ -7858,10 +8780,10 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>307</v>
+        <v>372</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>314</v>
+        <v>384</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>65</v>
@@ -7869,10 +8791,10 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
-        <v>307</v>
+        <v>372</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>308</v>
+        <v>373</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>65</v>
@@ -7880,10 +8802,10 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2" t="s">
-        <v>307</v>
+        <v>372</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>309</v>
+        <v>375</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>65</v>
@@ -7891,10 +8813,10 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2" t="s">
-        <v>280</v>
+        <v>336</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>277</v>
+        <v>332</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>65</v>
@@ -7902,10 +8824,10 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
-        <v>329</v>
+        <v>406</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>330</v>
+        <v>407</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>65</v>
@@ -7913,10 +8835,10 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2" t="s">
-        <v>329</v>
+        <v>406</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>331</v>
+        <v>409</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>65</v>
@@ -7924,10 +8846,10 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
-        <v>342</v>
+        <v>425</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>343</v>
+        <v>426</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>65</v>
@@ -7935,10 +8857,10 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2" t="s">
-        <v>342</v>
+        <v>425</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>345</v>
+        <v>429</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>65</v>
@@ -7946,10 +8868,10 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
-        <v>333</v>
+        <v>412</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>334</v>
+        <v>413</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>65</v>
@@ -7957,10 +8879,10 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
-        <v>333</v>
+        <v>412</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>337</v>
+        <v>417</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>65</v>
@@ -7968,10 +8890,10 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>338</v>
+        <v>419</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>339</v>
+        <v>420</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>65</v>
@@ -7979,10 +8901,10 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>338</v>
+        <v>419</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>341</v>
+        <v>423</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>65</v>
@@ -7990,10 +8912,10 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>266</v>
+        <v>317</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>267</v>
+        <v>318</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>65</v>
@@ -8001,10 +8923,10 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>268</v>
+        <v>320</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>269</v>
+        <v>321</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>65</v>
@@ -8012,10 +8934,10 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
-        <v>242</v>
+        <v>282</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>243</v>
+        <v>283</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>65</v>
@@ -8023,10 +8945,10 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2" t="s">
-        <v>246</v>
+        <v>288</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>247</v>
+        <v>289</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>65</v>
@@ -8034,10 +8956,10 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2" t="s">
-        <v>221</v>
+        <v>249</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>222</v>
+        <v>250</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>65</v>
@@ -8045,10 +8967,10 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2" t="s">
-        <v>221</v>
+        <v>249</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>224</v>
+        <v>253</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>65</v>
@@ -8056,10 +8978,10 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2" t="s">
-        <v>221</v>
+        <v>249</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>225</v>
+        <v>255</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>65</v>
@@ -8067,10 +8989,10 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="2" t="s">
-        <v>221</v>
+        <v>249</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>227</v>
+        <v>258</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>65</v>
@@ -8078,10 +9000,10 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2" t="s">
-        <v>221</v>
+        <v>249</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>228</v>
+        <v>260</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>65</v>
@@ -8089,10 +9011,10 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="2" t="s">
-        <v>221</v>
+        <v>249</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>229</v>
+        <v>262</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>65</v>
@@ -8100,10 +9022,10 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
-        <v>221</v>
+        <v>249</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>231</v>
+        <v>265</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>65</v>
@@ -8111,10 +9033,10 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2" t="s">
-        <v>238</v>
+        <v>276</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>239</v>
+        <v>277</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>65</v>
@@ -8122,10 +9044,10 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="2" t="s">
-        <v>319</v>
+        <v>392</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>320</v>
+        <v>393</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>65</v>
@@ -8133,10 +9055,10 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="2" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>225</v>
+        <v>255</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>65</v>
@@ -8144,10 +9066,10 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="2" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>229</v>
+        <v>262</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>65</v>
@@ -8155,10 +9077,10 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="2" t="s">
-        <v>281</v>
+        <v>337</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>277</v>
+        <v>332</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>65</v>
@@ -8166,10 +9088,10 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="2" t="s">
-        <v>252</v>
+        <v>297</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>253</v>
+        <v>298</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>65</v>
@@ -8177,10 +9099,10 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="2" t="s">
-        <v>282</v>
+        <v>338</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>277</v>
+        <v>332</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>65</v>
@@ -8188,10 +9110,10 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="2" t="s">
-        <v>346</v>
+        <v>431</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>347</v>
+        <v>432</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>65</v>
@@ -8199,10 +9121,10 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="2" t="s">
-        <v>205</v>
+        <v>224</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>206</v>
+        <v>225</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>65</v>
@@ -8210,10 +9132,10 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="2" t="s">
-        <v>298</v>
+        <v>358</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>299</v>
+        <v>359</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>65</v>
@@ -8221,10 +9143,10 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="2" t="s">
-        <v>298</v>
+        <v>358</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>300</v>
+        <v>361</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>65</v>
@@ -8232,10 +9154,10 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="2" t="s">
-        <v>298</v>
+        <v>358</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>301</v>
+        <v>363</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>65</v>
@@ -8243,10 +9165,10 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="2" t="s">
-        <v>298</v>
+        <v>358</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>302</v>
+        <v>365</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>65</v>
@@ -8254,10 +9176,10 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="2" t="s">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>65</v>
@@ -8265,10 +9187,10 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="2" t="s">
-        <v>323</v>
+        <v>398</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>324</v>
+        <v>399</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>65</v>
@@ -8276,10 +9198,10 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="2" t="s">
-        <v>325</v>
+        <v>401</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>326</v>
+        <v>402</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>65</v>
@@ -8287,10 +9209,10 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="2" t="s">
-        <v>327</v>
+        <v>404</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>326</v>
+        <v>402</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>65</v>
@@ -8298,10 +9220,10 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="2" t="s">
-        <v>328</v>
+        <v>405</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>326</v>
+        <v>402</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>65</v>
@@ -8309,7 +9231,7 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="2" t="s">
-        <v>352</v>
+        <v>440</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>65</v>
@@ -8317,10 +9239,10 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="2" t="s">
-        <v>283</v>
+        <v>339</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>277</v>
+        <v>332</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>65</v>
@@ -8328,10 +9250,10 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="2" t="s">
-        <v>315</v>
+        <v>386</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>316</v>
+        <v>387</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>65</v>
@@ -8339,10 +9261,10 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="2" t="s">
-        <v>223</v>
+        <v>252</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>222</v>
+        <v>250</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>65</v>
@@ -8350,10 +9272,10 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="2" t="s">
-        <v>223</v>
+        <v>252</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>224</v>
+        <v>253</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>65</v>
@@ -8361,10 +9283,10 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="2" t="s">
-        <v>223</v>
+        <v>252</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>227</v>
+        <v>258</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>65</v>
@@ -8372,10 +9294,10 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="2" t="s">
-        <v>223</v>
+        <v>252</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>228</v>
+        <v>260</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>65</v>
@@ -8383,10 +9305,10 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="2" t="s">
-        <v>296</v>
+        <v>355</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>297</v>
+        <v>356</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>65</v>
@@ -8394,10 +9316,10 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="2" t="s">
-        <v>293</v>
+        <v>351</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>294</v>
+        <v>352</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>65</v>
@@ -8405,10 +9327,10 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="2" t="s">
-        <v>211</v>
+        <v>234</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>212</v>
+        <v>235</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>65</v>
@@ -8416,10 +9338,10 @@
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="2" t="s">
-        <v>211</v>
+        <v>234</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>214</v>
+        <v>238</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>65</v>
@@ -8427,10 +9349,10 @@
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="2" t="s">
-        <v>211</v>
+        <v>234</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>215</v>
+        <v>240</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>65</v>
@@ -8438,10 +9360,10 @@
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="2" t="s">
-        <v>213</v>
+        <v>237</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>212</v>
+        <v>235</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>65</v>
@@ -8449,10 +9371,10 @@
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="2" t="s">
-        <v>213</v>
+        <v>237</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>214</v>
+        <v>238</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>65</v>
@@ -8460,10 +9382,10 @@
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="2" t="s">
-        <v>213</v>
+        <v>237</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>215</v>
+        <v>240</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>65</v>
@@ -8471,10 +9393,10 @@
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="2" t="s">
-        <v>216</v>
+        <v>242</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>217</v>
+        <v>243</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>65</v>
@@ -8482,10 +9404,10 @@
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="2" t="s">
-        <v>332</v>
+        <v>411</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>331</v>
+        <v>409</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>65</v>
@@ -8493,10 +9415,10 @@
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="2" t="s">
-        <v>234</v>
+        <v>270</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>235</v>
+        <v>271</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>65</v>
@@ -8504,10 +9426,10 @@
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="2" t="s">
-        <v>270</v>
+        <v>323</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>271</v>
+        <v>324</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>65</v>
@@ -8515,10 +9437,10 @@
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="2" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>208</v>
+        <v>228</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>65</v>
@@ -8526,10 +9448,10 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="2" t="s">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>65</v>
@@ -8537,10 +9459,10 @@
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="2" t="s">
-        <v>274</v>
+        <v>328</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>275</v>
+        <v>329</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>65</v>
@@ -8548,10 +9470,10 @@
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="2" t="s">
-        <v>232</v>
+        <v>267</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>233</v>
+        <v>268</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>65</v>
@@ -8559,10 +9481,10 @@
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="2" t="s">
-        <v>236</v>
+        <v>273</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>237</v>
+        <v>274</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>65</v>
@@ -8570,10 +9492,10 @@
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="2" t="s">
-        <v>284</v>
+        <v>340</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>277</v>
+        <v>332</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>65</v>
@@ -8581,10 +9503,10 @@
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="2" t="s">
-        <v>218</v>
+        <v>245</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>219</v>
+        <v>246</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>65</v>
@@ -8592,10 +9514,10 @@
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="2" t="s">
-        <v>220</v>
+        <v>248</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>219</v>
+        <v>246</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>65</v>
@@ -8603,10 +9525,10 @@
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="2" t="s">
-        <v>250</v>
+        <v>294</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>251</v>
+        <v>295</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>65</v>
@@ -8614,10 +9536,10 @@
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="2" t="s">
-        <v>248</v>
+        <v>291</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>249</v>
+        <v>292</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>65</v>
@@ -8625,10 +9547,10 @@
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="2" t="s">
-        <v>285</v>
+        <v>341</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>277</v>
+        <v>332</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>65</v>
@@ -8636,10 +9558,10 @@
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="2" t="s">
-        <v>286</v>
+        <v>342</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>277</v>
+        <v>332</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>65</v>
@@ -8647,10 +9569,10 @@
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="2" t="s">
-        <v>287</v>
+        <v>343</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>277</v>
+        <v>332</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>65</v>
@@ -8658,10 +9580,10 @@
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="2" t="s">
-        <v>288</v>
+        <v>344</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>277</v>
+        <v>332</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>65</v>
@@ -8669,10 +9591,10 @@
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="2" t="s">
-        <v>289</v>
+        <v>345</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>277</v>
+        <v>332</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>65</v>
@@ -8680,10 +9602,10 @@
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="2" t="s">
-        <v>335</v>
+        <v>415</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>334</v>
+        <v>413</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>65</v>
@@ -8691,10 +9613,10 @@
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="2" t="s">
-        <v>335</v>
+        <v>415</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>339</v>
+        <v>420</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>65</v>
@@ -8702,10 +9624,10 @@
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="2" t="s">
-        <v>335</v>
+        <v>415</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>343</v>
+        <v>426</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>65</v>
@@ -8713,10 +9635,10 @@
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="2" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>65</v>
@@ -8724,10 +9646,10 @@
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="2" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>65</v>
@@ -8735,10 +9657,10 @@
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="2" t="s">
-        <v>344</v>
+        <v>428</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>343</v>
+        <v>426</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>65</v>
@@ -8746,10 +9668,10 @@
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="2" t="s">
-        <v>344</v>
+        <v>428</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>345</v>
+        <v>429</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>65</v>
@@ -8757,10 +9679,10 @@
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="2" t="s">
-        <v>336</v>
+        <v>416</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>334</v>
+        <v>413</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>65</v>
@@ -8768,10 +9690,10 @@
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="2" t="s">
-        <v>336</v>
+        <v>416</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>337</v>
+        <v>417</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>65</v>
@@ -8779,10 +9701,10 @@
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="2" t="s">
-        <v>340</v>
+        <v>422</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>339</v>
+        <v>420</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>65</v>
@@ -8790,10 +9712,10 @@
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="2" t="s">
-        <v>340</v>
+        <v>422</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>341</v>
+        <v>423</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>65</v>
@@ -8801,7 +9723,7 @@
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="2" t="s">
-        <v>418</v>
+        <v>551</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>100</v>
@@ -8809,7 +9731,7 @@
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="2" t="s">
-        <v>419</v>
+        <v>552</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>100</v>
@@ -8817,7 +9739,7 @@
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="2" t="s">
-        <v>420</v>
+        <v>553</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>100</v>
@@ -8825,7 +9747,7 @@
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="2" t="s">
-        <v>421</v>
+        <v>554</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>100</v>
@@ -8833,7 +9755,7 @@
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="2" t="s">
-        <v>422</v>
+        <v>555</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>100</v>
@@ -8841,7 +9763,7 @@
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="2" t="s">
-        <v>423</v>
+        <v>556</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>100</v>
@@ -8849,10 +9771,10 @@
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="2" t="s">
-        <v>356</v>
+        <v>446</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>357</v>
+        <v>447</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>100</v>
@@ -8860,10 +9782,10 @@
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="2" t="s">
-        <v>356</v>
+        <v>446</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>358</v>
+        <v>449</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>100</v>
@@ -8871,10 +9793,10 @@
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="2" t="s">
-        <v>356</v>
+        <v>446</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>369</v>
+        <v>466</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>100</v>
@@ -8882,10 +9804,10 @@
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="2" t="s">
-        <v>356</v>
+        <v>446</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>370</v>
+        <v>470</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>100</v>
@@ -8893,10 +9815,10 @@
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="2" t="s">
-        <v>359</v>
+        <v>451</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>360</v>
+        <v>452</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>100</v>
@@ -8904,10 +9826,10 @@
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="2" t="s">
-        <v>371</v>
+        <v>472</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>372</v>
+        <v>473</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>100</v>
@@ -8915,10 +9837,10 @@
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="2" t="s">
-        <v>371</v>
+        <v>472</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>373</v>
+        <v>475</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>100</v>
@@ -8926,10 +9848,10 @@
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="2" t="s">
-        <v>374</v>
+        <v>477</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>375</v>
+        <v>478</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>100</v>
@@ -8937,10 +9859,10 @@
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="2" t="s">
-        <v>374</v>
+        <v>477</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>376</v>
+        <v>480</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>100</v>
@@ -8948,7 +9870,7 @@
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="2" t="s">
-        <v>424</v>
+        <v>557</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>100</v>
@@ -8956,7 +9878,7 @@
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="2" t="s">
-        <v>425</v>
+        <v>558</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>100</v>
@@ -8964,7 +9886,7 @@
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="2" t="s">
-        <v>426</v>
+        <v>559</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>100</v>
@@ -8972,7 +9894,7 @@
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="2" t="s">
-        <v>427</v>
+        <v>560</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>100</v>
@@ -8980,7 +9902,7 @@
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="2" t="s">
-        <v>428</v>
+        <v>561</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>100</v>
@@ -8988,10 +9910,10 @@
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="2" t="s">
-        <v>365</v>
+        <v>460</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>366</v>
+        <v>461</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>100</v>
@@ -8999,10 +9921,10 @@
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="2" t="s">
-        <v>367</v>
+        <v>463</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>368</v>
+        <v>464</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>100</v>
@@ -9010,10 +9932,10 @@
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="2" t="s">
-        <v>353</v>
+        <v>441</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>354</v>
+        <v>442</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>100</v>
@@ -9021,10 +9943,10 @@
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="2" t="s">
-        <v>353</v>
+        <v>441</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>355</v>
+        <v>444</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>100</v>
@@ -9032,10 +9954,10 @@
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="2" t="s">
-        <v>377</v>
+        <v>482</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>378</v>
+        <v>483</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>100</v>
@@ -9043,10 +9965,10 @@
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="2" t="s">
-        <v>377</v>
+        <v>482</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>379</v>
+        <v>485</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>100</v>
@@ -9054,10 +9976,10 @@
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="2" t="s">
-        <v>384</v>
+        <v>494</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>385</v>
+        <v>495</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>100</v>
@@ -9065,7 +9987,7 @@
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="2" t="s">
-        <v>429</v>
+        <v>562</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>100</v>
@@ -9073,10 +9995,10 @@
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="2" t="s">
-        <v>386</v>
+        <v>497</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>387</v>
+        <v>498</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>100</v>
@@ -9084,10 +10006,10 @@
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="2" t="s">
-        <v>386</v>
+        <v>497</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>388</v>
+        <v>500</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>100</v>
@@ -9095,7 +10017,7 @@
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="2" t="s">
-        <v>430</v>
+        <v>563</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>100</v>
@@ -9103,10 +10025,10 @@
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="2" t="s">
-        <v>361</v>
+        <v>454</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>362</v>
+        <v>455</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>100</v>
@@ -9114,10 +10036,10 @@
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="2" t="s">
-        <v>363</v>
+        <v>457</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>364</v>
+        <v>458</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>100</v>
@@ -9125,10 +10047,10 @@
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="2" t="s">
-        <v>400</v>
+        <v>519</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>401</v>
+        <v>520</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>100</v>
@@ -9136,10 +10058,10 @@
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="2" t="s">
-        <v>400</v>
+        <v>519</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>402</v>
+        <v>522</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>100</v>
@@ -9147,7 +10069,7 @@
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="2" t="s">
-        <v>431</v>
+        <v>564</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>100</v>
@@ -9155,10 +10077,10 @@
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="2" t="s">
-        <v>393</v>
+        <v>508</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>394</v>
+        <v>509</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>100</v>
@@ -9166,10 +10088,10 @@
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="2" t="s">
-        <v>389</v>
+        <v>502</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>390</v>
+        <v>503</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>100</v>
@@ -9177,10 +10099,10 @@
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="2" t="s">
-        <v>395</v>
+        <v>511</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>396</v>
+        <v>512</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>100</v>
@@ -9188,10 +10110,10 @@
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="2" t="s">
-        <v>395</v>
+        <v>511</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>397</v>
+        <v>514</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>100</v>
@@ -9199,7 +10121,7 @@
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="2" t="s">
-        <v>432</v>
+        <v>565</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>100</v>
@@ -9207,10 +10129,10 @@
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="2" t="s">
-        <v>398</v>
+        <v>516</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>399</v>
+        <v>517</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>100</v>
@@ -9218,10 +10140,10 @@
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="2" t="s">
-        <v>403</v>
+        <v>524</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>404</v>
+        <v>525</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>100</v>
@@ -9229,10 +10151,10 @@
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="2" t="s">
-        <v>403</v>
+        <v>524</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>405</v>
+        <v>527</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>100</v>
@@ -9240,10 +10162,10 @@
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="2" t="s">
-        <v>403</v>
+        <v>524</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>406</v>
+        <v>529</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>100</v>
@@ -9251,10 +10173,10 @@
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="2" t="s">
-        <v>403</v>
+        <v>524</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>407</v>
+        <v>531</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>100</v>
@@ -9262,10 +10184,10 @@
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="2" t="s">
-        <v>403</v>
+        <v>524</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>408</v>
+        <v>533</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>100</v>
@@ -9273,10 +10195,10 @@
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="2" t="s">
-        <v>403</v>
+        <v>524</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>409</v>
+        <v>535</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>100</v>
@@ -9284,10 +10206,10 @@
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="2" t="s">
-        <v>403</v>
+        <v>524</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>410</v>
+        <v>537</v>
       </c>
       <c r="C168" s="2" t="s">
         <v>100</v>
@@ -9295,10 +10217,10 @@
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="2" t="s">
-        <v>403</v>
+        <v>524</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>411</v>
+        <v>539</v>
       </c>
       <c r="C169" s="2" t="s">
         <v>100</v>
@@ -9306,10 +10228,10 @@
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="2" t="s">
-        <v>403</v>
+        <v>524</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>412</v>
+        <v>541</v>
       </c>
       <c r="C170" s="2" t="s">
         <v>100</v>
@@ -9317,10 +10239,10 @@
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="2" t="s">
-        <v>413</v>
+        <v>543</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>414</v>
+        <v>544</v>
       </c>
       <c r="C171" s="2" t="s">
         <v>100</v>
@@ -9328,10 +10250,10 @@
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="2" t="s">
-        <v>415</v>
+        <v>546</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>416</v>
+        <v>547</v>
       </c>
       <c r="C172" s="2" t="s">
         <v>100</v>
@@ -9339,7 +10261,7 @@
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="2" t="s">
-        <v>433</v>
+        <v>566</v>
       </c>
       <c r="C173" s="2" t="s">
         <v>100</v>
@@ -9347,10 +10269,10 @@
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="2" t="s">
-        <v>380</v>
+        <v>487</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>381</v>
+        <v>488</v>
       </c>
       <c r="C174" s="2" t="s">
         <v>100</v>
@@ -9358,10 +10280,10 @@
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="2" t="s">
-        <v>380</v>
+        <v>487</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>382</v>
+        <v>490</v>
       </c>
       <c r="C175" s="2" t="s">
         <v>100</v>
@@ -9369,10 +10291,10 @@
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="2" t="s">
-        <v>380</v>
+        <v>487</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>383</v>
+        <v>492</v>
       </c>
       <c r="C176" s="2" t="s">
         <v>100</v>
@@ -9380,10 +10302,10 @@
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="2" t="s">
-        <v>391</v>
+        <v>505</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>392</v>
+        <v>506</v>
       </c>
       <c r="C177" s="2" t="s">
         <v>100</v>
@@ -9391,7 +10313,7 @@
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="2" t="s">
-        <v>434</v>
+        <v>567</v>
       </c>
       <c r="C178" s="2" t="s">
         <v>100</v>
@@ -9399,7 +10321,7 @@
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="2" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="C179" s="2" t="s">
         <v>20</v>
@@ -9407,7 +10329,7 @@
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="2" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="C180" s="2" t="s">
         <v>20</v>
@@ -9415,7 +10337,7 @@
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="2" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="C181" s="2" t="s">
         <v>20</v>
@@ -9423,7 +10345,7 @@
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="2" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="C182" s="2" t="s">
         <v>20</v>
@@ -9431,7 +10353,7 @@
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="2" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="C183" s="2" t="s">
         <v>20</v>
@@ -9439,7 +10361,7 @@
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="2" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="C184" s="2" t="s">
         <v>20</v>
@@ -9447,7 +10369,7 @@
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="2" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="C185" s="2" t="s">
         <v>20</v>
@@ -9455,7 +10377,7 @@
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="2" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="C186" s="2" t="s">
         <v>20</v>
@@ -9463,10 +10385,10 @@
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="2" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>625</v>
+        <v>758</v>
       </c>
       <c r="C187" s="2" t="s">
         <v>20</v>
@@ -9474,10 +10396,10 @@
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="2" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>625</v>
+        <v>758</v>
       </c>
       <c r="C188" s="2" t="s">
         <v>20</v>
@@ -9485,7 +10407,7 @@
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="2" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="C189" s="2" t="s">
         <v>20</v>
@@ -9493,10 +10415,10 @@
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="2" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>626</v>
+        <v>759</v>
       </c>
       <c r="C190" s="2" t="s">
         <v>20</v>
@@ -9504,7 +10426,7 @@
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="2" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="C191" s="2" t="s">
         <v>20</v>
@@ -9512,7 +10434,7 @@
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="2" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="C192" s="2" t="s">
         <v>20</v>
@@ -9520,10 +10442,10 @@
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>627</v>
+        <v>760</v>
       </c>
       <c r="C193" s="2" t="s">
         <v>20</v>
@@ -9531,7 +10453,7 @@
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="2" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="C194" s="2" t="s">
         <v>20</v>
@@ -9539,10 +10461,10 @@
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="2" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>628</v>
+        <v>761</v>
       </c>
       <c r="C195" s="2" t="s">
         <v>20</v>
@@ -9550,10 +10472,10 @@
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>629</v>
+        <v>762</v>
       </c>
       <c r="C196" s="2" t="s">
         <v>20</v>
@@ -9561,10 +10483,10 @@
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="2" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>630</v>
+        <v>763</v>
       </c>
       <c r="C197" s="2" t="s">
         <v>20</v>
